--- a/Client/Tables/G_MissionInfoTable.xlsx
+++ b/Client/Tables/G_MissionInfoTable.xlsx
@@ -24722,9 +24722,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Client/Tables/G_MissionInfoTable.xlsx
+++ b/Client/Tables/G_MissionInfoTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="194">
   <si>
     <t>식별자 범위</t>
   </si>
@@ -107,7 +107,7 @@
     <t>아이템 강화</t>
   </si>
   <si>
-    <t>이어하기</t>
+    <t>재배치</t>
   </si>
   <si>
     <t>경험치</t>
@@ -116,7 +116,7 @@
     <t>값 타입</t>
   </si>
   <si>
-    <t>재배치</t>
+    <t>이어하기 - 1</t>
   </si>
   <si>
     <t>경험치 증가</t>
@@ -134,7 +134,7 @@
     <t>스킬 레벨</t>
   </si>
   <si>
-    <t>광고 제거</t>
+    <t>결제</t>
   </si>
   <si>
     <t>실수</t>
@@ -143,10 +143,16 @@
     <t>스킬 경험치</t>
   </si>
   <si>
+    <t>광고 시청</t>
+  </si>
+  <si>
     <t>개수</t>
   </si>
   <si>
     <t>스킬 개수</t>
+  </si>
+  <si>
+    <t>광고 제거</t>
   </si>
   <si>
     <t>개수 증가</t>
@@ -798,14 +804,14 @@
     <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="13" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="13" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
@@ -1595,8 +1601,12 @@
       <c r="L11" s="19">
         <v>1.000002E8</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="20"/>
+      <c r="M11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="20">
+        <v>2.00000001E8</v>
+      </c>
       <c r="O11" s="8"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="9"/>
@@ -1604,7 +1614,7 @@
       <c r="S11" s="10"/>
       <c r="T11" s="23"/>
       <c r="U11" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V11" s="24">
         <v>200.0</v>
@@ -1631,13 +1641,17 @@
       <c r="I12" s="5"/>
       <c r="J12" s="18"/>
       <c r="K12" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L12" s="19">
         <v>1.000003E8</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="20"/>
+      <c r="M12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="20">
+        <v>2.00000002E8</v>
+      </c>
       <c r="O12" s="8"/>
       <c r="P12" s="21"/>
       <c r="Q12" s="9"/>
@@ -1645,7 +1659,7 @@
       <c r="S12" s="10"/>
       <c r="T12" s="23"/>
       <c r="U12" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="V12" s="24">
         <v>1.00002E7</v>
@@ -1662,7 +1676,7 @@
     </row>
     <row r="13">
       <c r="A13" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="2"/>
@@ -1674,7 +1688,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="18"/>
       <c r="K13" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L13" s="19">
         <v>1.000004E8</v>
@@ -1688,7 +1702,7 @@
       <c r="S13" s="10"/>
       <c r="T13" s="23"/>
       <c r="U13" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V13" s="24">
         <v>2.00002E7</v>
@@ -1742,7 +1756,7 @@
     </row>
     <row r="15">
       <c r="A15" s="26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="14">
         <v>0.0</v>
@@ -1756,7 +1770,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="18"/>
       <c r="K15" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L15" s="19">
         <v>2.0E8</v>
@@ -1770,7 +1784,7 @@
       <c r="S15" s="10"/>
       <c r="T15" s="23"/>
       <c r="U15" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="V15" s="24">
         <v>300.0</v>
@@ -1787,7 +1801,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" s="14">
         <v>1.0</v>
@@ -1801,7 +1815,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="18"/>
       <c r="K16" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L16" s="19">
         <v>2.000001E8</v>
@@ -1815,7 +1829,7 @@
       <c r="S16" s="10"/>
       <c r="T16" s="23"/>
       <c r="U16" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="V16" s="24">
         <v>1.00003E7</v>
@@ -1832,7 +1846,7 @@
     </row>
     <row r="17">
       <c r="A17" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" s="14">
         <v>2.0</v>
@@ -1846,7 +1860,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="18"/>
       <c r="K17" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="19">
         <v>2.000002E8</v>
@@ -1860,7 +1874,7 @@
       <c r="S17" s="10"/>
       <c r="T17" s="23"/>
       <c r="U17" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V17" s="24">
         <v>2.00003E7</v>
@@ -1887,7 +1901,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="18"/>
       <c r="K18" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L18" s="19">
         <v>2.000003E8</v>
@@ -1914,7 +1928,7 @@
     </row>
     <row r="19">
       <c r="A19" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="2"/>
@@ -1926,7 +1940,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="18"/>
       <c r="K19" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L19" s="19">
         <v>2.000004E8</v>
@@ -1940,7 +1954,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="23"/>
       <c r="U19" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V19" s="24">
         <v>100000.0</v>
@@ -1981,7 +1995,7 @@
       <c r="S20" s="10"/>
       <c r="T20" s="23"/>
       <c r="U20" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="V20" s="24">
         <v>100001.0</v>
@@ -2012,7 +2026,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="18"/>
       <c r="K21" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L21" s="19">
         <v>3.0E8</v>
@@ -2026,7 +2040,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="23"/>
       <c r="U21" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V21" s="24">
         <v>1.01E7</v>
@@ -2057,7 +2071,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="18"/>
       <c r="K22" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L22" s="19">
         <v>3.000001E8</v>
@@ -2071,7 +2085,7 @@
       <c r="S22" s="10"/>
       <c r="T22" s="23"/>
       <c r="U22" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V22" s="24">
         <v>2.01E7</v>
@@ -2088,7 +2102,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="14">
         <v>2.0</v>
@@ -2125,7 +2139,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B24" s="14">
         <v>3.0</v>
@@ -2149,7 +2163,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="23"/>
       <c r="U24" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V24" s="24">
         <v>100100.0</v>
@@ -2186,7 +2200,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="23"/>
       <c r="U25" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="V25" s="24">
         <v>100101.0</v>
@@ -2203,7 +2217,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="2"/>
@@ -2225,7 +2239,7 @@
       <c r="S26" s="10"/>
       <c r="T26" s="23"/>
       <c r="U26" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="V26" s="24">
         <v>1.01001E7</v>
@@ -2266,7 +2280,7 @@
       <c r="S27" s="10"/>
       <c r="T27" s="23"/>
       <c r="U27" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="V27" s="24">
         <v>2.01001E7</v>
@@ -2283,7 +2297,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B28" s="14">
         <v>0.0</v>
@@ -2320,7 +2334,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B29" s="14">
         <v>1.0</v>
@@ -2344,7 +2358,7 @@
       <c r="S29" s="10"/>
       <c r="T29" s="23"/>
       <c r="U29" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V29" s="24">
         <v>100200.0</v>
@@ -2361,7 +2375,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B30" s="14">
         <v>2.0</v>
@@ -2385,7 +2399,7 @@
       <c r="S30" s="10"/>
       <c r="T30" s="23"/>
       <c r="U30" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V30" s="24">
         <v>100201.0</v>
@@ -2422,7 +2436,7 @@
       <c r="S31" s="10"/>
       <c r="T31" s="23"/>
       <c r="U31" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V31" s="24">
         <v>1.01002E7</v>
@@ -2459,7 +2473,7 @@
       <c r="S32" s="10"/>
       <c r="T32" s="23"/>
       <c r="U32" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V32" s="24">
         <v>2.01002E7</v>
@@ -2529,7 +2543,7 @@
       <c r="S34" s="10"/>
       <c r="T34" s="23"/>
       <c r="U34" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="V34" s="24">
         <v>200000.0</v>
@@ -2566,7 +2580,7 @@
       <c r="S35" s="10"/>
       <c r="T35" s="23"/>
       <c r="U35" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V35" s="24">
         <v>200001.0</v>
@@ -2603,7 +2617,7 @@
       <c r="S36" s="10"/>
       <c r="T36" s="23"/>
       <c r="U36" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V36" s="24">
         <v>1.02E7</v>
@@ -2640,7 +2654,7 @@
       <c r="S37" s="10"/>
       <c r="T37" s="23"/>
       <c r="U37" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="V37" s="24">
         <v>2.02E7</v>
@@ -2710,7 +2724,7 @@
       <c r="S39" s="10"/>
       <c r="T39" s="23"/>
       <c r="U39" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="V39" s="24">
         <v>200100.0</v>
@@ -2747,7 +2761,7 @@
       <c r="S40" s="10"/>
       <c r="T40" s="23"/>
       <c r="U40" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V40" s="24">
         <v>200101.0</v>
@@ -2784,7 +2798,7 @@
       <c r="S41" s="10"/>
       <c r="T41" s="23"/>
       <c r="U41" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V41" s="24">
         <v>1.02001E7</v>
@@ -2821,7 +2835,7 @@
       <c r="S42" s="10"/>
       <c r="T42" s="23"/>
       <c r="U42" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V42" s="24">
         <v>2.02001E7</v>
@@ -2891,7 +2905,7 @@
       <c r="S44" s="10"/>
       <c r="T44" s="23"/>
       <c r="U44" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="V44" s="24">
         <v>200200.0</v>
@@ -2928,7 +2942,7 @@
       <c r="S45" s="10"/>
       <c r="T45" s="23"/>
       <c r="U45" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V45" s="24">
         <v>200201.0</v>
@@ -2965,7 +2979,7 @@
       <c r="S46" s="10"/>
       <c r="T46" s="23"/>
       <c r="U46" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V46" s="24">
         <v>1.02002E7</v>
@@ -3002,7 +3016,7 @@
       <c r="S47" s="10"/>
       <c r="T47" s="23"/>
       <c r="U47" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="V47" s="24">
         <v>2.02002E7</v>
@@ -3072,7 +3086,7 @@
       <c r="S49" s="10"/>
       <c r="T49" s="23"/>
       <c r="U49" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V49" s="24">
         <v>200300.0</v>
@@ -3109,7 +3123,7 @@
       <c r="S50" s="10"/>
       <c r="T50" s="23"/>
       <c r="U50" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V50" s="24">
         <v>200301.0</v>
@@ -3146,7 +3160,7 @@
       <c r="S51" s="10"/>
       <c r="T51" s="23"/>
       <c r="U51" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V51" s="24">
         <v>1.02003E7</v>
@@ -3183,7 +3197,7 @@
       <c r="S52" s="10"/>
       <c r="T52" s="23"/>
       <c r="U52" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V52" s="24">
         <v>2.02003E7</v>
@@ -3253,7 +3267,7 @@
       <c r="S54" s="10"/>
       <c r="T54" s="23"/>
       <c r="U54" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="V54" s="24">
         <v>300000.0</v>
@@ -3290,7 +3304,7 @@
       <c r="S55" s="10"/>
       <c r="T55" s="23"/>
       <c r="U55" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="V55" s="24">
         <v>300001.0</v>
@@ -3327,7 +3341,7 @@
       <c r="S56" s="10"/>
       <c r="T56" s="23"/>
       <c r="U56" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="V56" s="24">
         <v>1.03E7</v>
@@ -3364,7 +3378,7 @@
       <c r="S57" s="10"/>
       <c r="T57" s="23"/>
       <c r="U57" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="V57" s="24">
         <v>2.03E7</v>
@@ -3434,7 +3448,7 @@
       <c r="S59" s="10"/>
       <c r="T59" s="23"/>
       <c r="U59" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V59" s="24">
         <v>300100.0</v>
@@ -3471,7 +3485,7 @@
       <c r="S60" s="10"/>
       <c r="T60" s="23"/>
       <c r="U60" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V60" s="24">
         <v>300101.0</v>
@@ -3508,7 +3522,7 @@
       <c r="S61" s="10"/>
       <c r="T61" s="23"/>
       <c r="U61" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V61" s="24">
         <v>1.03001E7</v>
@@ -3545,7 +3559,7 @@
       <c r="S62" s="10"/>
       <c r="T62" s="23"/>
       <c r="U62" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V62" s="24">
         <v>2.03001E7</v>
@@ -3615,7 +3629,7 @@
       <c r="S64" s="10"/>
       <c r="T64" s="23"/>
       <c r="U64" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V64" s="24">
         <v>300200.0</v>
@@ -3652,7 +3666,7 @@
       <c r="S65" s="10"/>
       <c r="T65" s="23"/>
       <c r="U65" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V65" s="24">
         <v>300201.0</v>
@@ -3689,7 +3703,7 @@
       <c r="S66" s="10"/>
       <c r="T66" s="23"/>
       <c r="U66" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="V66" s="24">
         <v>1.03002E7</v>
@@ -3726,7 +3740,7 @@
       <c r="S67" s="10"/>
       <c r="T67" s="23"/>
       <c r="U67" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V67" s="24">
         <v>2.03002E7</v>
@@ -3796,7 +3810,7 @@
       <c r="S69" s="10"/>
       <c r="T69" s="23"/>
       <c r="U69" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V69" s="24">
         <v>400000.0</v>
@@ -3833,7 +3847,7 @@
       <c r="S70" s="10"/>
       <c r="T70" s="23"/>
       <c r="U70" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V70" s="24">
         <v>400001.0</v>
@@ -3870,7 +3884,7 @@
       <c r="S71" s="10"/>
       <c r="T71" s="23"/>
       <c r="U71" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V71" s="24">
         <v>1.04E7</v>
@@ -3907,7 +3921,7 @@
       <c r="S72" s="10"/>
       <c r="T72" s="23"/>
       <c r="U72" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V72" s="24">
         <v>2.04E7</v>
@@ -3977,7 +3991,7 @@
       <c r="S74" s="10"/>
       <c r="T74" s="23"/>
       <c r="U74" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V74" s="24">
         <v>400100.0</v>
@@ -4014,7 +4028,7 @@
       <c r="S75" s="10"/>
       <c r="T75" s="23"/>
       <c r="U75" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V75" s="24">
         <v>400101.0</v>
@@ -4051,7 +4065,7 @@
       <c r="S76" s="10"/>
       <c r="T76" s="23"/>
       <c r="U76" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="V76" s="24">
         <v>1.04001E7</v>
@@ -4088,7 +4102,7 @@
       <c r="S77" s="10"/>
       <c r="T77" s="23"/>
       <c r="U77" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V77" s="24">
         <v>2.04001E7</v>
@@ -4158,7 +4172,7 @@
       <c r="S79" s="10"/>
       <c r="T79" s="23"/>
       <c r="U79" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="V79" s="24">
         <v>400200.0</v>
@@ -4195,7 +4209,7 @@
       <c r="S80" s="10"/>
       <c r="T80" s="23"/>
       <c r="U80" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V80" s="24">
         <v>400201.0</v>
@@ -4232,7 +4246,7 @@
       <c r="S81" s="10"/>
       <c r="T81" s="23"/>
       <c r="U81" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V81" s="24">
         <v>1.04002E7</v>
@@ -4269,7 +4283,7 @@
       <c r="S82" s="10"/>
       <c r="T82" s="23"/>
       <c r="U82" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V82" s="24">
         <v>2.04002E7</v>
@@ -4339,7 +4353,7 @@
       <c r="S84" s="10"/>
       <c r="T84" s="23"/>
       <c r="U84" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V84" s="24">
         <v>500000.0</v>
@@ -4376,7 +4390,7 @@
       <c r="S85" s="10"/>
       <c r="T85" s="23"/>
       <c r="U85" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V85" s="24">
         <v>500001.0</v>
@@ -4413,7 +4427,7 @@
       <c r="S86" s="10"/>
       <c r="T86" s="23"/>
       <c r="U86" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="V86" s="24">
         <v>1.05E7</v>
@@ -4450,7 +4464,7 @@
       <c r="S87" s="10"/>
       <c r="T87" s="23"/>
       <c r="U87" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V87" s="24">
         <v>2.05E7</v>
@@ -4520,7 +4534,7 @@
       <c r="S89" s="10"/>
       <c r="T89" s="23"/>
       <c r="U89" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="V89" s="24">
         <v>500100.0</v>
@@ -4557,7 +4571,7 @@
       <c r="S90" s="10"/>
       <c r="T90" s="23"/>
       <c r="U90" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V90" s="24">
         <v>500101.0</v>
@@ -4594,7 +4608,7 @@
       <c r="S91" s="10"/>
       <c r="T91" s="23"/>
       <c r="U91" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="V91" s="24">
         <v>1.05001E7</v>
@@ -4631,7 +4645,7 @@
       <c r="S92" s="10"/>
       <c r="T92" s="23"/>
       <c r="U92" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V92" s="24">
         <v>2.05001E7</v>
@@ -4701,7 +4715,7 @@
       <c r="S94" s="10"/>
       <c r="T94" s="23"/>
       <c r="U94" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="V94" s="24">
         <v>500200.0</v>
@@ -4738,7 +4752,7 @@
       <c r="S95" s="10"/>
       <c r="T95" s="23"/>
       <c r="U95" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V95" s="24">
         <v>500201.0</v>
@@ -4775,7 +4789,7 @@
       <c r="S96" s="10"/>
       <c r="T96" s="23"/>
       <c r="U96" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V96" s="24">
         <v>1.05002E7</v>
@@ -4812,7 +4826,7 @@
       <c r="S97" s="10"/>
       <c r="T97" s="23"/>
       <c r="U97" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V97" s="24">
         <v>2.05002E7</v>
@@ -4882,7 +4896,7 @@
       <c r="S99" s="10"/>
       <c r="T99" s="23"/>
       <c r="U99" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="V99" s="24">
         <v>600000.0</v>
@@ -4919,7 +4933,7 @@
       <c r="S100" s="10"/>
       <c r="T100" s="23"/>
       <c r="U100" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="V100" s="24">
         <v>600001.0</v>
@@ -4956,7 +4970,7 @@
       <c r="S101" s="10"/>
       <c r="T101" s="23"/>
       <c r="U101" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="V101" s="24">
         <v>1.06E7</v>
@@ -4993,7 +5007,7 @@
       <c r="S102" s="10"/>
       <c r="T102" s="23"/>
       <c r="U102" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="V102" s="24">
         <v>2.06E7</v>
@@ -5063,7 +5077,7 @@
       <c r="S104" s="10"/>
       <c r="T104" s="23"/>
       <c r="U104" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="V104" s="24">
         <v>600100.0</v>
@@ -5100,7 +5114,7 @@
       <c r="S105" s="10"/>
       <c r="T105" s="23"/>
       <c r="U105" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="V105" s="24">
         <v>600101.0</v>
@@ -5137,7 +5151,7 @@
       <c r="S106" s="10"/>
       <c r="T106" s="23"/>
       <c r="U106" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="V106" s="24">
         <v>1.06001E7</v>
@@ -5174,7 +5188,7 @@
       <c r="S107" s="10"/>
       <c r="T107" s="23"/>
       <c r="U107" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="V107" s="24">
         <v>2.06001E7</v>
@@ -5244,7 +5258,7 @@
       <c r="S109" s="10"/>
       <c r="T109" s="23"/>
       <c r="U109" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="V109" s="24">
         <v>600200.0</v>
@@ -5281,7 +5295,7 @@
       <c r="S110" s="10"/>
       <c r="T110" s="23"/>
       <c r="U110" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="V110" s="24">
         <v>600201.0</v>
@@ -5318,7 +5332,7 @@
       <c r="S111" s="10"/>
       <c r="T111" s="23"/>
       <c r="U111" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V111" s="24">
         <v>1.06002E7</v>
@@ -5355,7 +5369,7 @@
       <c r="S112" s="10"/>
       <c r="T112" s="23"/>
       <c r="U112" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="V112" s="24">
         <v>2.06002E7</v>
@@ -5425,7 +5439,7 @@
       <c r="S114" s="10"/>
       <c r="T114" s="23"/>
       <c r="U114" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="V114" s="24">
         <v>700000.0</v>
@@ -5462,7 +5476,7 @@
       <c r="S115" s="10"/>
       <c r="T115" s="23"/>
       <c r="U115" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="V115" s="24">
         <v>700001.0</v>
@@ -5499,7 +5513,7 @@
       <c r="S116" s="10"/>
       <c r="T116" s="23"/>
       <c r="U116" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="V116" s="24">
         <v>1.07E7</v>
@@ -5536,7 +5550,7 @@
       <c r="S117" s="10"/>
       <c r="T117" s="23"/>
       <c r="U117" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="V117" s="24">
         <v>2.07E7</v>
@@ -5606,7 +5620,7 @@
       <c r="S119" s="10"/>
       <c r="T119" s="23"/>
       <c r="U119" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V119" s="24">
         <v>700100.0</v>
@@ -5643,7 +5657,7 @@
       <c r="S120" s="10"/>
       <c r="T120" s="23"/>
       <c r="U120" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="V120" s="24">
         <v>700101.0</v>
@@ -5680,7 +5694,7 @@
       <c r="S121" s="10"/>
       <c r="T121" s="23"/>
       <c r="U121" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="V121" s="24">
         <v>1.07001E7</v>
@@ -5717,7 +5731,7 @@
       <c r="S122" s="10"/>
       <c r="T122" s="23"/>
       <c r="U122" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="V122" s="24">
         <v>2.07001E7</v>
@@ -5787,7 +5801,7 @@
       <c r="S124" s="10"/>
       <c r="T124" s="23"/>
       <c r="U124" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="V124" s="24">
         <v>700200.0</v>
@@ -5824,7 +5838,7 @@
       <c r="S125" s="10"/>
       <c r="T125" s="23"/>
       <c r="U125" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V125" s="24">
         <v>700201.0</v>
@@ -5861,7 +5875,7 @@
       <c r="S126" s="10"/>
       <c r="T126" s="23"/>
       <c r="U126" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="V126" s="24">
         <v>1.07002E7</v>
@@ -5898,7 +5912,7 @@
       <c r="S127" s="10"/>
       <c r="T127" s="23"/>
       <c r="U127" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="V127" s="24">
         <v>2.07002E7</v>
@@ -5968,7 +5982,7 @@
       <c r="S129" s="10"/>
       <c r="T129" s="23"/>
       <c r="U129" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="V129" s="24">
         <v>800000.0</v>
@@ -6005,7 +6019,7 @@
       <c r="S130" s="10"/>
       <c r="T130" s="23"/>
       <c r="U130" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="V130" s="24">
         <v>800001.0</v>
@@ -6042,7 +6056,7 @@
       <c r="S131" s="10"/>
       <c r="T131" s="23"/>
       <c r="U131" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="V131" s="24">
         <v>1.08E7</v>
@@ -6079,7 +6093,7 @@
       <c r="S132" s="10"/>
       <c r="T132" s="23"/>
       <c r="U132" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="V132" s="24">
         <v>2.08E7</v>
@@ -6149,7 +6163,7 @@
       <c r="S134" s="10"/>
       <c r="T134" s="23"/>
       <c r="U134" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V134" s="24">
         <v>800100.0</v>
@@ -6186,7 +6200,7 @@
       <c r="S135" s="10"/>
       <c r="T135" s="23"/>
       <c r="U135" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="V135" s="24">
         <v>800101.0</v>
@@ -6223,7 +6237,7 @@
       <c r="S136" s="10"/>
       <c r="T136" s="23"/>
       <c r="U136" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="V136" s="24">
         <v>1.08001E7</v>
@@ -6260,7 +6274,7 @@
       <c r="S137" s="10"/>
       <c r="T137" s="23"/>
       <c r="U137" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="V137" s="24">
         <v>2.08001E7</v>
@@ -6330,7 +6344,7 @@
       <c r="S139" s="10"/>
       <c r="T139" s="23"/>
       <c r="U139" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V139" s="24">
         <v>800200.0</v>
@@ -6367,7 +6381,7 @@
       <c r="S140" s="10"/>
       <c r="T140" s="23"/>
       <c r="U140" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="V140" s="24">
         <v>800201.0</v>
@@ -6404,7 +6418,7 @@
       <c r="S141" s="10"/>
       <c r="T141" s="23"/>
       <c r="U141" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V141" s="24">
         <v>1.08002E7</v>
@@ -6441,7 +6455,7 @@
       <c r="S142" s="10"/>
       <c r="T142" s="23"/>
       <c r="U142" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V142" s="24">
         <v>2.08002E7</v>
@@ -6511,7 +6525,7 @@
       <c r="S144" s="10"/>
       <c r="T144" s="23"/>
       <c r="U144" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="V144" s="24">
         <v>800300.0</v>
@@ -6548,7 +6562,7 @@
       <c r="S145" s="10"/>
       <c r="T145" s="23"/>
       <c r="U145" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="V145" s="24">
         <v>800301.0</v>
@@ -6585,7 +6599,7 @@
       <c r="S146" s="10"/>
       <c r="T146" s="23"/>
       <c r="U146" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="V146" s="24">
         <v>1.08003E7</v>
@@ -6622,7 +6636,7 @@
       <c r="S147" s="10"/>
       <c r="T147" s="23"/>
       <c r="U147" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="V147" s="24">
         <v>2.08003E7</v>
@@ -13156,659 +13170,2618 @@
       <c r="U347" s="31"/>
       <c r="V347" s="31"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="M348" s="32"/>
+      <c r="N348" s="32"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="M349" s="32"/>
+      <c r="N349" s="32"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="M350" s="32"/>
+      <c r="N350" s="32"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="M351" s="32"/>
+      <c r="N351" s="32"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="M352" s="32"/>
+      <c r="N352" s="32"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="M353" s="32"/>
+      <c r="N353" s="32"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="M354" s="32"/>
+      <c r="N354" s="32"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="M355" s="32"/>
+      <c r="N355" s="32"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="M356" s="32"/>
+      <c r="N356" s="32"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="M357" s="32"/>
+      <c r="N357" s="32"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="M358" s="32"/>
+      <c r="N358" s="32"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="M359" s="32"/>
+      <c r="N359" s="32"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="M360" s="32"/>
+      <c r="N360" s="32"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="M361" s="32"/>
+      <c r="N361" s="32"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="M362" s="32"/>
+      <c r="N362" s="32"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="M363" s="32"/>
+      <c r="N363" s="32"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="M364" s="32"/>
+      <c r="N364" s="32"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="M365" s="32"/>
+      <c r="N365" s="32"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="M366" s="32"/>
+      <c r="N366" s="32"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="M367" s="32"/>
+      <c r="N367" s="32"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="M368" s="32"/>
+      <c r="N368" s="32"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="M369" s="32"/>
+      <c r="N369" s="32"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="M370" s="32"/>
+      <c r="N370" s="32"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="M371" s="32"/>
+      <c r="N371" s="32"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="M372" s="32"/>
+      <c r="N372" s="32"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="M373" s="32"/>
+      <c r="N373" s="32"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="M374" s="32"/>
+      <c r="N374" s="32"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="M375" s="32"/>
+      <c r="N375" s="32"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="M376" s="32"/>
+      <c r="N376" s="32"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="M377" s="32"/>
+      <c r="N377" s="32"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="M378" s="32"/>
+      <c r="N378" s="32"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="M379" s="32"/>
+      <c r="N379" s="32"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="M380" s="32"/>
+      <c r="N380" s="32"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="M381" s="32"/>
+      <c r="N381" s="32"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="M382" s="32"/>
+      <c r="N382" s="32"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="M383" s="32"/>
+      <c r="N383" s="32"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="M384" s="32"/>
+      <c r="N384" s="32"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="M385" s="32"/>
+      <c r="N385" s="32"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="M386" s="32"/>
+      <c r="N386" s="32"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="M387" s="32"/>
+      <c r="N387" s="32"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="M388" s="32"/>
+      <c r="N388" s="32"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="M389" s="32"/>
+      <c r="N389" s="32"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="M390" s="32"/>
+      <c r="N390" s="32"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="M391" s="32"/>
+      <c r="N391" s="32"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="M392" s="32"/>
+      <c r="N392" s="32"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="M393" s="32"/>
+      <c r="N393" s="32"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="M394" s="32"/>
+      <c r="N394" s="32"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="M395" s="32"/>
+      <c r="N395" s="32"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="M396" s="32"/>
+      <c r="N396" s="32"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="M397" s="32"/>
+      <c r="N397" s="32"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="M398" s="32"/>
+      <c r="N398" s="32"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="M399" s="32"/>
+      <c r="N399" s="32"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="M400" s="32"/>
+      <c r="N400" s="32"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="M401" s="32"/>
+      <c r="N401" s="32"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="M402" s="32"/>
+      <c r="N402" s="32"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="M403" s="32"/>
+      <c r="N403" s="32"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="M404" s="32"/>
+      <c r="N404" s="32"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="M405" s="32"/>
+      <c r="N405" s="32"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="M406" s="32"/>
+      <c r="N406" s="32"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="M407" s="32"/>
+      <c r="N407" s="32"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="M408" s="32"/>
+      <c r="N408" s="32"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="M409" s="32"/>
+      <c r="N409" s="32"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="M410" s="32"/>
+      <c r="N410" s="32"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="M411" s="32"/>
+      <c r="N411" s="32"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="M412" s="32"/>
+      <c r="N412" s="32"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="M413" s="32"/>
+      <c r="N413" s="32"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="M414" s="32"/>
+      <c r="N414" s="32"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="M415" s="32"/>
+      <c r="N415" s="32"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="M416" s="32"/>
+      <c r="N416" s="32"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="M417" s="32"/>
+      <c r="N417" s="32"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="M418" s="32"/>
+      <c r="N418" s="32"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="M419" s="32"/>
+      <c r="N419" s="32"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="M420" s="32"/>
+      <c r="N420" s="32"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="M421" s="32"/>
+      <c r="N421" s="32"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="M422" s="32"/>
+      <c r="N422" s="32"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="M423" s="32"/>
+      <c r="N423" s="32"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="M424" s="32"/>
+      <c r="N424" s="32"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="M425" s="32"/>
+      <c r="N425" s="32"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="M426" s="32"/>
+      <c r="N426" s="32"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="M427" s="32"/>
+      <c r="N427" s="32"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="M428" s="32"/>
+      <c r="N428" s="32"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="M429" s="32"/>
+      <c r="N429" s="32"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="M430" s="32"/>
+      <c r="N430" s="32"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="M431" s="32"/>
+      <c r="N431" s="32"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="M432" s="32"/>
+      <c r="N432" s="32"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="M433" s="32"/>
+      <c r="N433" s="32"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="M434" s="32"/>
+      <c r="N434" s="32"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="M435" s="32"/>
+      <c r="N435" s="32"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="M436" s="32"/>
+      <c r="N436" s="32"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="M437" s="32"/>
+      <c r="N437" s="32"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="M438" s="32"/>
+      <c r="N438" s="32"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="M439" s="32"/>
+      <c r="N439" s="32"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="M440" s="32"/>
+      <c r="N440" s="32"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="M441" s="32"/>
+      <c r="N441" s="32"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="M442" s="32"/>
+      <c r="N442" s="32"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="M443" s="32"/>
+      <c r="N443" s="32"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="M444" s="32"/>
+      <c r="N444" s="32"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="M445" s="32"/>
+      <c r="N445" s="32"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="M446" s="32"/>
+      <c r="N446" s="32"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="M447" s="32"/>
+      <c r="N447" s="32"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="M448" s="32"/>
+      <c r="N448" s="32"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="M449" s="32"/>
+      <c r="N449" s="32"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="M450" s="32"/>
+      <c r="N450" s="32"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="M451" s="32"/>
+      <c r="N451" s="32"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="M452" s="32"/>
+      <c r="N452" s="32"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="M453" s="32"/>
+      <c r="N453" s="32"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="M454" s="32"/>
+      <c r="N454" s="32"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="M455" s="32"/>
+      <c r="N455" s="32"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="M456" s="32"/>
+      <c r="N456" s="32"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="M457" s="32"/>
+      <c r="N457" s="32"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="M458" s="32"/>
+      <c r="N458" s="32"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="M459" s="32"/>
+      <c r="N459" s="32"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="M460" s="32"/>
+      <c r="N460" s="32"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="M461" s="32"/>
+      <c r="N461" s="32"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="M462" s="32"/>
+      <c r="N462" s="32"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="M463" s="32"/>
+      <c r="N463" s="32"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="M464" s="32"/>
+      <c r="N464" s="32"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="M465" s="32"/>
+      <c r="N465" s="32"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="M466" s="32"/>
+      <c r="N466" s="32"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="M467" s="32"/>
+      <c r="N467" s="32"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="M468" s="32"/>
+      <c r="N468" s="32"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="M469" s="32"/>
+      <c r="N469" s="32"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="M470" s="32"/>
+      <c r="N470" s="32"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="M471" s="32"/>
+      <c r="N471" s="32"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="M472" s="32"/>
+      <c r="N472" s="32"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="M473" s="32"/>
+      <c r="N473" s="32"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="M474" s="32"/>
+      <c r="N474" s="32"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="M475" s="32"/>
+      <c r="N475" s="32"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="M476" s="32"/>
+      <c r="N476" s="32"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="M477" s="32"/>
+      <c r="N477" s="32"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="M478" s="32"/>
+      <c r="N478" s="32"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="M479" s="32"/>
+      <c r="N479" s="32"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="M480" s="32"/>
+      <c r="N480" s="32"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="M481" s="32"/>
+      <c r="N481" s="32"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="M482" s="32"/>
+      <c r="N482" s="32"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="M483" s="32"/>
+      <c r="N483" s="32"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="M484" s="32"/>
+      <c r="N484" s="32"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="M485" s="32"/>
+      <c r="N485" s="32"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="M486" s="32"/>
+      <c r="N486" s="32"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="M487" s="32"/>
+      <c r="N487" s="32"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="M488" s="32"/>
+      <c r="N488" s="32"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="M489" s="32"/>
+      <c r="N489" s="32"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="M490" s="32"/>
+      <c r="N490" s="32"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="M491" s="32"/>
+      <c r="N491" s="32"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="M492" s="32"/>
+      <c r="N492" s="32"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="M493" s="32"/>
+      <c r="N493" s="32"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="M494" s="32"/>
+      <c r="N494" s="32"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="M495" s="32"/>
+      <c r="N495" s="32"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="M496" s="32"/>
+      <c r="N496" s="32"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="M497" s="32"/>
+      <c r="N497" s="32"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="M498" s="32"/>
+      <c r="N498" s="32"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="M499" s="32"/>
+      <c r="N499" s="32"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="M500" s="32"/>
+      <c r="N500" s="32"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="M501" s="32"/>
+      <c r="N501" s="32"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="M502" s="32"/>
+      <c r="N502" s="32"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="M503" s="32"/>
+      <c r="N503" s="32"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="M504" s="32"/>
+      <c r="N504" s="32"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="M505" s="32"/>
+      <c r="N505" s="32"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="M506" s="32"/>
+      <c r="N506" s="32"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="M507" s="32"/>
+      <c r="N507" s="32"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="M508" s="32"/>
+      <c r="N508" s="32"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="M509" s="32"/>
+      <c r="N509" s="32"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="M510" s="32"/>
+      <c r="N510" s="32"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="M511" s="32"/>
+      <c r="N511" s="32"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="M512" s="32"/>
+      <c r="N512" s="32"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="M513" s="32"/>
+      <c r="N513" s="32"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="M514" s="32"/>
+      <c r="N514" s="32"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="M515" s="32"/>
+      <c r="N515" s="32"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="M516" s="32"/>
+      <c r="N516" s="32"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="M517" s="32"/>
+      <c r="N517" s="32"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="M518" s="32"/>
+      <c r="N518" s="32"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="M519" s="32"/>
+      <c r="N519" s="32"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="M520" s="32"/>
+      <c r="N520" s="32"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="M521" s="32"/>
+      <c r="N521" s="32"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="M522" s="32"/>
+      <c r="N522" s="32"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="M523" s="32"/>
+      <c r="N523" s="32"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="M524" s="32"/>
+      <c r="N524" s="32"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="M525" s="32"/>
+      <c r="N525" s="32"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="M526" s="32"/>
+      <c r="N526" s="32"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="M527" s="32"/>
+      <c r="N527" s="32"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="M528" s="32"/>
+      <c r="N528" s="32"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="M529" s="32"/>
+      <c r="N529" s="32"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="M530" s="32"/>
+      <c r="N530" s="32"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="M531" s="32"/>
+      <c r="N531" s="32"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="M532" s="32"/>
+      <c r="N532" s="32"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="M533" s="32"/>
+      <c r="N533" s="32"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="M534" s="32"/>
+      <c r="N534" s="32"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="M535" s="32"/>
+      <c r="N535" s="32"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="M536" s="32"/>
+      <c r="N536" s="32"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="M537" s="32"/>
+      <c r="N537" s="32"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="M538" s="32"/>
+      <c r="N538" s="32"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="M539" s="32"/>
+      <c r="N539" s="32"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="M540" s="32"/>
+      <c r="N540" s="32"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="M541" s="32"/>
+      <c r="N541" s="32"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="M542" s="32"/>
+      <c r="N542" s="32"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="M543" s="32"/>
+      <c r="N543" s="32"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="M544" s="32"/>
+      <c r="N544" s="32"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="M545" s="32"/>
+      <c r="N545" s="32"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="M546" s="32"/>
+      <c r="N546" s="32"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="M547" s="32"/>
+      <c r="N547" s="32"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="M548" s="32"/>
+      <c r="N548" s="32"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="M549" s="32"/>
+      <c r="N549" s="32"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="M550" s="32"/>
+      <c r="N550" s="32"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="M551" s="32"/>
+      <c r="N551" s="32"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="M552" s="32"/>
+      <c r="N552" s="32"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="M553" s="32"/>
+      <c r="N553" s="32"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="M554" s="32"/>
+      <c r="N554" s="32"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="M555" s="32"/>
+      <c r="N555" s="32"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="M556" s="32"/>
+      <c r="N556" s="32"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="M557" s="32"/>
+      <c r="N557" s="32"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="M558" s="32"/>
+      <c r="N558" s="32"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="M559" s="32"/>
+      <c r="N559" s="32"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="M560" s="32"/>
+      <c r="N560" s="32"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="M561" s="32"/>
+      <c r="N561" s="32"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="M562" s="32"/>
+      <c r="N562" s="32"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="M563" s="32"/>
+      <c r="N563" s="32"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="M564" s="32"/>
+      <c r="N564" s="32"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="M565" s="32"/>
+      <c r="N565" s="32"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="M566" s="32"/>
+      <c r="N566" s="32"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="M567" s="32"/>
+      <c r="N567" s="32"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="M568" s="32"/>
+      <c r="N568" s="32"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="M569" s="32"/>
+      <c r="N569" s="32"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="M570" s="32"/>
+      <c r="N570" s="32"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="M571" s="32"/>
+      <c r="N571" s="32"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="M572" s="32"/>
+      <c r="N572" s="32"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="M573" s="32"/>
+      <c r="N573" s="32"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="M574" s="32"/>
+      <c r="N574" s="32"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="M575" s="32"/>
+      <c r="N575" s="32"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="M576" s="32"/>
+      <c r="N576" s="32"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="M577" s="32"/>
+      <c r="N577" s="32"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="M578" s="32"/>
+      <c r="N578" s="32"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="M579" s="32"/>
+      <c r="N579" s="32"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="M580" s="32"/>
+      <c r="N580" s="32"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="M581" s="32"/>
+      <c r="N581" s="32"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="M582" s="32"/>
+      <c r="N582" s="32"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="M583" s="32"/>
+      <c r="N583" s="32"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="M584" s="32"/>
+      <c r="N584" s="32"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="M585" s="32"/>
+      <c r="N585" s="32"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="M586" s="32"/>
+      <c r="N586" s="32"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="M587" s="32"/>
+      <c r="N587" s="32"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="M588" s="32"/>
+      <c r="N588" s="32"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="M589" s="32"/>
+      <c r="N589" s="32"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="M590" s="32"/>
+      <c r="N590" s="32"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="M591" s="32"/>
+      <c r="N591" s="32"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="M592" s="32"/>
+      <c r="N592" s="32"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="M593" s="32"/>
+      <c r="N593" s="32"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="M594" s="32"/>
+      <c r="N594" s="32"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="M595" s="32"/>
+      <c r="N595" s="32"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="M596" s="32"/>
+      <c r="N596" s="32"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="M597" s="32"/>
+      <c r="N597" s="32"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="M598" s="32"/>
+      <c r="N598" s="32"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="M599" s="32"/>
+      <c r="N599" s="32"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="M600" s="32"/>
+      <c r="N600" s="32"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="M601" s="32"/>
+      <c r="N601" s="32"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="M602" s="32"/>
+      <c r="N602" s="32"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="M603" s="32"/>
+      <c r="N603" s="32"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="M604" s="32"/>
+      <c r="N604" s="32"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="M605" s="32"/>
+      <c r="N605" s="32"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="M606" s="32"/>
+      <c r="N606" s="32"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="M607" s="32"/>
+      <c r="N607" s="32"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="M608" s="32"/>
+      <c r="N608" s="32"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="M609" s="32"/>
+      <c r="N609" s="32"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="M610" s="32"/>
+      <c r="N610" s="32"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="M611" s="32"/>
+      <c r="N611" s="32"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="M612" s="32"/>
+      <c r="N612" s="32"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="M613" s="32"/>
+      <c r="N613" s="32"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="M614" s="32"/>
+      <c r="N614" s="32"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="M615" s="32"/>
+      <c r="N615" s="32"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="M616" s="32"/>
+      <c r="N616" s="32"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="M617" s="32"/>
+      <c r="N617" s="32"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="M618" s="32"/>
+      <c r="N618" s="32"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="M619" s="32"/>
+      <c r="N619" s="32"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="M620" s="32"/>
+      <c r="N620" s="32"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="M621" s="32"/>
+      <c r="N621" s="32"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="M622" s="32"/>
+      <c r="N622" s="32"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="M623" s="32"/>
+      <c r="N623" s="32"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="M624" s="32"/>
+      <c r="N624" s="32"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="M625" s="32"/>
+      <c r="N625" s="32"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="M626" s="32"/>
+      <c r="N626" s="32"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="M627" s="32"/>
+      <c r="N627" s="32"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="M628" s="32"/>
+      <c r="N628" s="32"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="M629" s="32"/>
+      <c r="N629" s="32"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="M630" s="32"/>
+      <c r="N630" s="32"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="M631" s="32"/>
+      <c r="N631" s="32"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="M632" s="32"/>
+      <c r="N632" s="32"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="M633" s="32"/>
+      <c r="N633" s="32"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="M634" s="32"/>
+      <c r="N634" s="32"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="M635" s="32"/>
+      <c r="N635" s="32"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="M636" s="32"/>
+      <c r="N636" s="32"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="M637" s="32"/>
+      <c r="N637" s="32"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="M638" s="32"/>
+      <c r="N638" s="32"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="M639" s="32"/>
+      <c r="N639" s="32"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="M640" s="32"/>
+      <c r="N640" s="32"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="M641" s="32"/>
+      <c r="N641" s="32"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="M642" s="32"/>
+      <c r="N642" s="32"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="M643" s="32"/>
+      <c r="N643" s="32"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="M644" s="32"/>
+      <c r="N644" s="32"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="M645" s="32"/>
+      <c r="N645" s="32"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="M646" s="32"/>
+      <c r="N646" s="32"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="M647" s="32"/>
+      <c r="N647" s="32"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="M648" s="32"/>
+      <c r="N648" s="32"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="M649" s="32"/>
+      <c r="N649" s="32"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="M650" s="32"/>
+      <c r="N650" s="32"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="M651" s="32"/>
+      <c r="N651" s="32"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="M652" s="32"/>
+      <c r="N652" s="32"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="M653" s="32"/>
+      <c r="N653" s="32"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="M654" s="32"/>
+      <c r="N654" s="32"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="M655" s="32"/>
+      <c r="N655" s="32"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="M656" s="32"/>
+      <c r="N656" s="32"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="M657" s="32"/>
+      <c r="N657" s="32"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="M658" s="32"/>
+      <c r="N658" s="32"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="M659" s="32"/>
+      <c r="N659" s="32"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="M660" s="32"/>
+      <c r="N660" s="32"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="M661" s="32"/>
+      <c r="N661" s="32"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="M662" s="32"/>
+      <c r="N662" s="32"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="M663" s="32"/>
+      <c r="N663" s="32"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="M664" s="32"/>
+      <c r="N664" s="32"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="M665" s="32"/>
+      <c r="N665" s="32"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="M666" s="32"/>
+      <c r="N666" s="32"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="M667" s="32"/>
+      <c r="N667" s="32"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="M668" s="32"/>
+      <c r="N668" s="32"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="M669" s="32"/>
+      <c r="N669" s="32"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="M670" s="32"/>
+      <c r="N670" s="32"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="M671" s="32"/>
+      <c r="N671" s="32"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="M672" s="32"/>
+      <c r="N672" s="32"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="M673" s="32"/>
+      <c r="N673" s="32"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="M674" s="32"/>
+      <c r="N674" s="32"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="M675" s="32"/>
+      <c r="N675" s="32"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="M676" s="32"/>
+      <c r="N676" s="32"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="M677" s="32"/>
+      <c r="N677" s="32"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="M678" s="32"/>
+      <c r="N678" s="32"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="M679" s="32"/>
+      <c r="N679" s="32"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="M680" s="32"/>
+      <c r="N680" s="32"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="M681" s="32"/>
+      <c r="N681" s="32"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="M682" s="32"/>
+      <c r="N682" s="32"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="M683" s="32"/>
+      <c r="N683" s="32"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="M684" s="32"/>
+      <c r="N684" s="32"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="M685" s="32"/>
+      <c r="N685" s="32"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="M686" s="32"/>
+      <c r="N686" s="32"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="M687" s="32"/>
+      <c r="N687" s="32"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="M688" s="32"/>
+      <c r="N688" s="32"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="M689" s="32"/>
+      <c r="N689" s="32"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="M690" s="32"/>
+      <c r="N690" s="32"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="M691" s="32"/>
+      <c r="N691" s="32"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="M692" s="32"/>
+      <c r="N692" s="32"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="M693" s="32"/>
+      <c r="N693" s="32"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="M694" s="32"/>
+      <c r="N694" s="32"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="M695" s="32"/>
+      <c r="N695" s="32"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="M696" s="32"/>
+      <c r="N696" s="32"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="M697" s="32"/>
+      <c r="N697" s="32"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="M698" s="32"/>
+      <c r="N698" s="32"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="M699" s="32"/>
+      <c r="N699" s="32"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="M700" s="32"/>
+      <c r="N700" s="32"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="M701" s="32"/>
+      <c r="N701" s="32"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="M702" s="32"/>
+      <c r="N702" s="32"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="M703" s="32"/>
+      <c r="N703" s="32"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="M704" s="32"/>
+      <c r="N704" s="32"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="M705" s="32"/>
+      <c r="N705" s="32"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="M706" s="32"/>
+      <c r="N706" s="32"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="M707" s="32"/>
+      <c r="N707" s="32"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="M708" s="32"/>
+      <c r="N708" s="32"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="M709" s="32"/>
+      <c r="N709" s="32"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="M710" s="32"/>
+      <c r="N710" s="32"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="M711" s="32"/>
+      <c r="N711" s="32"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="M712" s="32"/>
+      <c r="N712" s="32"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="M713" s="32"/>
+      <c r="N713" s="32"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="M714" s="32"/>
+      <c r="N714" s="32"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="M715" s="32"/>
+      <c r="N715" s="32"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="M716" s="32"/>
+      <c r="N716" s="32"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="M717" s="32"/>
+      <c r="N717" s="32"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="M718" s="32"/>
+      <c r="N718" s="32"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="M719" s="32"/>
+      <c r="N719" s="32"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="M720" s="32"/>
+      <c r="N720" s="32"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="M721" s="32"/>
+      <c r="N721" s="32"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="M722" s="32"/>
+      <c r="N722" s="32"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="M723" s="32"/>
+      <c r="N723" s="32"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="M724" s="32"/>
+      <c r="N724" s="32"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="M725" s="32"/>
+      <c r="N725" s="32"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="M726" s="32"/>
+      <c r="N726" s="32"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="M727" s="32"/>
+      <c r="N727" s="32"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="M728" s="32"/>
+      <c r="N728" s="32"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="M729" s="32"/>
+      <c r="N729" s="32"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="M730" s="32"/>
+      <c r="N730" s="32"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="M731" s="32"/>
+      <c r="N731" s="32"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="M732" s="32"/>
+      <c r="N732" s="32"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="M733" s="32"/>
+      <c r="N733" s="32"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="M734" s="32"/>
+      <c r="N734" s="32"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="M735" s="32"/>
+      <c r="N735" s="32"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="M736" s="32"/>
+      <c r="N736" s="32"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="M737" s="32"/>
+      <c r="N737" s="32"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="M738" s="32"/>
+      <c r="N738" s="32"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="M739" s="32"/>
+      <c r="N739" s="32"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="M740" s="32"/>
+      <c r="N740" s="32"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="M741" s="32"/>
+      <c r="N741" s="32"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="M742" s="32"/>
+      <c r="N742" s="32"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="M743" s="32"/>
+      <c r="N743" s="32"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="M744" s="32"/>
+      <c r="N744" s="32"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="M745" s="32"/>
+      <c r="N745" s="32"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="M746" s="32"/>
+      <c r="N746" s="32"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="M747" s="32"/>
+      <c r="N747" s="32"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="M748" s="32"/>
+      <c r="N748" s="32"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="M749" s="32"/>
+      <c r="N749" s="32"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="M750" s="32"/>
+      <c r="N750" s="32"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="M751" s="32"/>
+      <c r="N751" s="32"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="M752" s="32"/>
+      <c r="N752" s="32"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="M753" s="32"/>
+      <c r="N753" s="32"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="M754" s="32"/>
+      <c r="N754" s="32"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="M755" s="32"/>
+      <c r="N755" s="32"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="M756" s="32"/>
+      <c r="N756" s="32"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="M757" s="32"/>
+      <c r="N757" s="32"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="M758" s="32"/>
+      <c r="N758" s="32"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="M759" s="32"/>
+      <c r="N759" s="32"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="M760" s="32"/>
+      <c r="N760" s="32"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="M761" s="32"/>
+      <c r="N761" s="32"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="M762" s="32"/>
+      <c r="N762" s="32"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="M763" s="32"/>
+      <c r="N763" s="32"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="M764" s="32"/>
+      <c r="N764" s="32"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="M765" s="32"/>
+      <c r="N765" s="32"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="M766" s="32"/>
+      <c r="N766" s="32"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="M767" s="32"/>
+      <c r="N767" s="32"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="M768" s="32"/>
+      <c r="N768" s="32"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="M769" s="32"/>
+      <c r="N769" s="32"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="M770" s="32"/>
+      <c r="N770" s="32"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="M771" s="32"/>
+      <c r="N771" s="32"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="M772" s="32"/>
+      <c r="N772" s="32"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="M773" s="32"/>
+      <c r="N773" s="32"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="M774" s="32"/>
+      <c r="N774" s="32"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="M775" s="32"/>
+      <c r="N775" s="32"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="M776" s="32"/>
+      <c r="N776" s="32"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="M777" s="32"/>
+      <c r="N777" s="32"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="M778" s="32"/>
+      <c r="N778" s="32"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="M779" s="32"/>
+      <c r="N779" s="32"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="M780" s="32"/>
+      <c r="N780" s="32"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="M781" s="32"/>
+      <c r="N781" s="32"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="M782" s="32"/>
+      <c r="N782" s="32"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="M783" s="32"/>
+      <c r="N783" s="32"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="M784" s="32"/>
+      <c r="N784" s="32"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="M785" s="32"/>
+      <c r="N785" s="32"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="M786" s="32"/>
+      <c r="N786" s="32"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="M787" s="32"/>
+      <c r="N787" s="32"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="M788" s="32"/>
+      <c r="N788" s="32"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="M789" s="32"/>
+      <c r="N789" s="32"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="M790" s="32"/>
+      <c r="N790" s="32"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="M791" s="32"/>
+      <c r="N791" s="32"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="M792" s="32"/>
+      <c r="N792" s="32"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="M793" s="32"/>
+      <c r="N793" s="32"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="M794" s="32"/>
+      <c r="N794" s="32"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="M795" s="32"/>
+      <c r="N795" s="32"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="M796" s="32"/>
+      <c r="N796" s="32"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="M797" s="32"/>
+      <c r="N797" s="32"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="M798" s="32"/>
+      <c r="N798" s="32"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="M799" s="32"/>
+      <c r="N799" s="32"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="M800" s="32"/>
+      <c r="N800" s="32"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="M801" s="32"/>
+      <c r="N801" s="32"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="M802" s="32"/>
+      <c r="N802" s="32"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="M803" s="32"/>
+      <c r="N803" s="32"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="M804" s="32"/>
+      <c r="N804" s="32"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="M805" s="32"/>
+      <c r="N805" s="32"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="M806" s="32"/>
+      <c r="N806" s="32"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="M807" s="32"/>
+      <c r="N807" s="32"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="M808" s="32"/>
+      <c r="N808" s="32"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="M809" s="32"/>
+      <c r="N809" s="32"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="M810" s="32"/>
+      <c r="N810" s="32"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="M811" s="32"/>
+      <c r="N811" s="32"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="M812" s="32"/>
+      <c r="N812" s="32"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="M813" s="32"/>
+      <c r="N813" s="32"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="M814" s="32"/>
+      <c r="N814" s="32"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="M815" s="32"/>
+      <c r="N815" s="32"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="M816" s="32"/>
+      <c r="N816" s="32"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="M817" s="32"/>
+      <c r="N817" s="32"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="M818" s="32"/>
+      <c r="N818" s="32"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="M819" s="32"/>
+      <c r="N819" s="32"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="M820" s="32"/>
+      <c r="N820" s="32"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="M821" s="32"/>
+      <c r="N821" s="32"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="M822" s="32"/>
+      <c r="N822" s="32"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="M823" s="32"/>
+      <c r="N823" s="32"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="M824" s="32"/>
+      <c r="N824" s="32"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="M825" s="32"/>
+      <c r="N825" s="32"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="M826" s="32"/>
+      <c r="N826" s="32"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="M827" s="32"/>
+      <c r="N827" s="32"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="M828" s="32"/>
+      <c r="N828" s="32"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="M829" s="32"/>
+      <c r="N829" s="32"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="M830" s="32"/>
+      <c r="N830" s="32"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="M831" s="32"/>
+      <c r="N831" s="32"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="M832" s="32"/>
+      <c r="N832" s="32"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="M833" s="32"/>
+      <c r="N833" s="32"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="M834" s="32"/>
+      <c r="N834" s="32"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="M835" s="32"/>
+      <c r="N835" s="32"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="M836" s="32"/>
+      <c r="N836" s="32"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="M837" s="32"/>
+      <c r="N837" s="32"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="M838" s="32"/>
+      <c r="N838" s="32"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="M839" s="32"/>
+      <c r="N839" s="32"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="M840" s="32"/>
+      <c r="N840" s="32"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="M841" s="32"/>
+      <c r="N841" s="32"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="M842" s="32"/>
+      <c r="N842" s="32"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="M843" s="32"/>
+      <c r="N843" s="32"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="M844" s="32"/>
+      <c r="N844" s="32"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="M845" s="32"/>
+      <c r="N845" s="32"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="M846" s="32"/>
+      <c r="N846" s="32"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="M847" s="32"/>
+      <c r="N847" s="32"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="M848" s="32"/>
+      <c r="N848" s="32"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="M849" s="32"/>
+      <c r="N849" s="32"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="M850" s="32"/>
+      <c r="N850" s="32"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="M851" s="32"/>
+      <c r="N851" s="32"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="M852" s="32"/>
+      <c r="N852" s="32"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="M853" s="32"/>
+      <c r="N853" s="32"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="M854" s="32"/>
+      <c r="N854" s="32"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="M855" s="32"/>
+      <c r="N855" s="32"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="M856" s="32"/>
+      <c r="N856" s="32"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="M857" s="32"/>
+      <c r="N857" s="32"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="M858" s="32"/>
+      <c r="N858" s="32"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="M859" s="32"/>
+      <c r="N859" s="32"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="M860" s="32"/>
+      <c r="N860" s="32"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="M861" s="32"/>
+      <c r="N861" s="32"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="M862" s="32"/>
+      <c r="N862" s="32"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="M863" s="32"/>
+      <c r="N863" s="32"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="M864" s="32"/>
+      <c r="N864" s="32"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="M865" s="32"/>
+      <c r="N865" s="32"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="M866" s="32"/>
+      <c r="N866" s="32"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="M867" s="32"/>
+      <c r="N867" s="32"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="M868" s="32"/>
+      <c r="N868" s="32"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="M869" s="32"/>
+      <c r="N869" s="32"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="M870" s="32"/>
+      <c r="N870" s="32"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="M871" s="32"/>
+      <c r="N871" s="32"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="M872" s="32"/>
+      <c r="N872" s="32"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="M873" s="32"/>
+      <c r="N873" s="32"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="M874" s="32"/>
+      <c r="N874" s="32"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="M875" s="32"/>
+      <c r="N875" s="32"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="M876" s="32"/>
+      <c r="N876" s="32"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="M877" s="32"/>
+      <c r="N877" s="32"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="M878" s="32"/>
+      <c r="N878" s="32"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="M879" s="32"/>
+      <c r="N879" s="32"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="M880" s="32"/>
+      <c r="N880" s="32"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="M881" s="32"/>
+      <c r="N881" s="32"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="M882" s="32"/>
+      <c r="N882" s="32"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="M883" s="32"/>
+      <c r="N883" s="32"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="M884" s="32"/>
+      <c r="N884" s="32"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="M885" s="32"/>
+      <c r="N885" s="32"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="M886" s="32"/>
+      <c r="N886" s="32"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="M887" s="32"/>
+      <c r="N887" s="32"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="M888" s="32"/>
+      <c r="N888" s="32"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="M889" s="32"/>
+      <c r="N889" s="32"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="M890" s="32"/>
+      <c r="N890" s="32"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="M891" s="32"/>
+      <c r="N891" s="32"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="M892" s="32"/>
+      <c r="N892" s="32"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="M893" s="32"/>
+      <c r="N893" s="32"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="M894" s="32"/>
+      <c r="N894" s="32"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="M895" s="32"/>
+      <c r="N895" s="32"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="M896" s="32"/>
+      <c r="N896" s="32"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="M897" s="32"/>
+      <c r="N897" s="32"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="M898" s="32"/>
+      <c r="N898" s="32"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="M899" s="32"/>
+      <c r="N899" s="32"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="M900" s="32"/>
+      <c r="N900" s="32"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="M901" s="32"/>
+      <c r="N901" s="32"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="M902" s="32"/>
+      <c r="N902" s="32"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="M903" s="32"/>
+      <c r="N903" s="32"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="M904" s="32"/>
+      <c r="N904" s="32"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="M905" s="32"/>
+      <c r="N905" s="32"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="M906" s="32"/>
+      <c r="N906" s="32"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="M907" s="32"/>
+      <c r="N907" s="32"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="M908" s="32"/>
+      <c r="N908" s="32"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="M909" s="32"/>
+      <c r="N909" s="32"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="M910" s="32"/>
+      <c r="N910" s="32"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="M911" s="32"/>
+      <c r="N911" s="32"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="M912" s="32"/>
+      <c r="N912" s="32"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="M913" s="32"/>
+      <c r="N913" s="32"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="M914" s="32"/>
+      <c r="N914" s="32"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="M915" s="32"/>
+      <c r="N915" s="32"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="M916" s="32"/>
+      <c r="N916" s="32"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="M917" s="32"/>
+      <c r="N917" s="32"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="M918" s="32"/>
+      <c r="N918" s="32"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="M919" s="32"/>
+      <c r="N919" s="32"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="M920" s="32"/>
+      <c r="N920" s="32"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="M921" s="32"/>
+      <c r="N921" s="32"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="M922" s="32"/>
+      <c r="N922" s="32"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="M923" s="32"/>
+      <c r="N923" s="32"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="M924" s="32"/>
+      <c r="N924" s="32"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="M925" s="32"/>
+      <c r="N925" s="32"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="M926" s="32"/>
+      <c r="N926" s="32"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="M927" s="32"/>
+      <c r="N927" s="32"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="M928" s="32"/>
+      <c r="N928" s="32"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="M929" s="32"/>
+      <c r="N929" s="32"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="M930" s="32"/>
+      <c r="N930" s="32"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="M931" s="32"/>
+      <c r="N931" s="32"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="M932" s="32"/>
+      <c r="N932" s="32"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="M933" s="32"/>
+      <c r="N933" s="32"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="M934" s="32"/>
+      <c r="N934" s="32"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="M935" s="32"/>
+      <c r="N935" s="32"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="M936" s="32"/>
+      <c r="N936" s="32"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="M937" s="32"/>
+      <c r="N937" s="32"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="M938" s="32"/>
+      <c r="N938" s="32"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="M939" s="32"/>
+      <c r="N939" s="32"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="M940" s="32"/>
+      <c r="N940" s="32"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="M941" s="32"/>
+      <c r="N941" s="32"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="M942" s="32"/>
+      <c r="N942" s="32"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="M943" s="32"/>
+      <c r="N943" s="32"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="M944" s="32"/>
+      <c r="N944" s="32"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="M945" s="32"/>
+      <c r="N945" s="32"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="M946" s="32"/>
+      <c r="N946" s="32"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="M947" s="32"/>
+      <c r="N947" s="32"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="M948" s="32"/>
+      <c r="N948" s="32"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="M949" s="32"/>
+      <c r="N949" s="32"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="M950" s="32"/>
+      <c r="N950" s="32"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="M951" s="32"/>
+      <c r="N951" s="32"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="M952" s="32"/>
+      <c r="N952" s="32"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="M953" s="32"/>
+      <c r="N953" s="32"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="M954" s="32"/>
+      <c r="N954" s="32"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="M955" s="32"/>
+      <c r="N955" s="32"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="M956" s="32"/>
+      <c r="N956" s="32"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="M957" s="32"/>
+      <c r="N957" s="32"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="M958" s="32"/>
+      <c r="N958" s="32"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="M959" s="32"/>
+      <c r="N959" s="32"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="M960" s="32"/>
+      <c r="N960" s="32"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="M961" s="32"/>
+      <c r="N961" s="32"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="M962" s="32"/>
+      <c r="N962" s="32"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="M963" s="32"/>
+      <c r="N963" s="32"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="M964" s="32"/>
+      <c r="N964" s="32"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="M965" s="32"/>
+      <c r="N965" s="32"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="M966" s="32"/>
+      <c r="N966" s="32"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="M967" s="32"/>
+      <c r="N967" s="32"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="M968" s="32"/>
+      <c r="N968" s="32"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="M969" s="32"/>
+      <c r="N969" s="32"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="M970" s="32"/>
+      <c r="N970" s="32"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="M971" s="32"/>
+      <c r="N971" s="32"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="M972" s="32"/>
+      <c r="N972" s="32"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="M973" s="32"/>
+      <c r="N973" s="32"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="M974" s="32"/>
+      <c r="N974" s="32"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="M975" s="32"/>
+      <c r="N975" s="32"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="M976" s="32"/>
+      <c r="N976" s="32"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="M977" s="32"/>
+      <c r="N977" s="32"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="M978" s="32"/>
+      <c r="N978" s="32"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="M979" s="32"/>
+      <c r="N979" s="32"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="M980" s="32"/>
+      <c r="N980" s="32"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="M981" s="32"/>
+      <c r="N981" s="32"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="M982" s="32"/>
+      <c r="N982" s="32"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="M983" s="32"/>
+      <c r="N983" s="32"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="M984" s="32"/>
+      <c r="N984" s="32"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="M985" s="32"/>
+      <c r="N985" s="32"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="M986" s="32"/>
+      <c r="N986" s="32"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="M987" s="32"/>
+      <c r="N987" s="32"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="M988" s="32"/>
+      <c r="N988" s="32"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="M989" s="32"/>
+      <c r="N989" s="32"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="M990" s="32"/>
+      <c r="N990" s="32"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="M991" s="32"/>
+      <c r="N991" s="32"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="M992" s="32"/>
+      <c r="N992" s="32"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="M993" s="32"/>
+      <c r="N993" s="32"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="M994" s="32"/>
+      <c r="N994" s="32"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="M995" s="32"/>
+      <c r="N995" s="32"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="M996" s="32"/>
+      <c r="N996" s="32"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="M997" s="32"/>
+      <c r="N997" s="32"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="M998" s="32"/>
+      <c r="N998" s="32"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1">
+      <c r="M999" s="32"/>
+      <c r="N999" s="32"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="M1000" s="32"/>
+      <c r="N1000" s="32"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -13839,77 +15812,77 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="L1" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="M1" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="N1" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="O1" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
+      <c r="P1" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
     </row>
     <row r="2">
       <c r="A2" s="35" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B2" s="36">
         <v>0.0</v>
@@ -13980,7 +15953,7 @@
     </row>
     <row r="3">
       <c r="A3" s="35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B3" s="36">
         <v>1.0</v>
@@ -14051,7 +16024,7 @@
     </row>
     <row r="4">
       <c r="A4" s="35" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" s="36">
         <v>2.0</v>
@@ -14121,8 +16094,8 @@
       <c r="AH4" s="37"/>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="s">
-        <v>191</v>
+      <c r="A5" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="B5" s="15">
         <v>3.0</v>
@@ -14151,8 +16124,8 @@
       <c r="J5" s="14">
         <v>0.0</v>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="14">
         <f>IF($A5="", -1, ($B5*README!$B$2)+($C5*README!$B$3)+($D5*README!$B$4)+($E5*README!$B$5)+($F5*README!$B$6))</f>
         <v>300000000</v>
@@ -14199,7 +16172,7 @@
       <c r="F6" s="40"/>
     </row>
     <row r="7">
-      <c r="A7" s="32"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -14209,8 +16182,8 @@
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="14"/>
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
@@ -14242,7 +16215,7 @@
       <c r="F8" s="40"/>
     </row>
     <row r="9">
-      <c r="A9" s="32"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -14252,8 +16225,8 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="39"/>
       <c r="N9" s="39"/>
       <c r="O9" s="39"/>
@@ -14278,7 +16251,7 @@
       <c r="AH9" s="39"/>
     </row>
     <row r="10">
-      <c r="A10" s="32"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -14288,8 +16261,8 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="39"/>
       <c r="N10" s="39"/>
       <c r="O10" s="39"/>
@@ -14314,7 +16287,7 @@
       <c r="AH10" s="39"/>
     </row>
     <row r="11">
-      <c r="A11" s="32"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -14324,8 +16297,8 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="39"/>
       <c r="N11" s="39"/>
       <c r="O11" s="39"/>
@@ -14350,7 +16323,7 @@
       <c r="AH11" s="39"/>
     </row>
     <row r="12">
-      <c r="A12" s="32"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -14360,8 +16333,8 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="39"/>
       <c r="N12" s="39"/>
       <c r="O12" s="39"/>
@@ -14386,7 +16359,7 @@
       <c r="AH12" s="39"/>
     </row>
     <row r="13">
-      <c r="A13" s="32"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -14396,8 +16369,8 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
       <c r="M13" s="39"/>
       <c r="N13" s="39"/>
       <c r="O13" s="39"/>
@@ -14422,7 +16395,7 @@
       <c r="AH13" s="39"/>
     </row>
     <row r="14">
-      <c r="A14" s="32"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -14432,8 +16405,8 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="39"/>
       <c r="N14" s="39"/>
       <c r="O14" s="39"/>
@@ -14458,7 +16431,7 @@
       <c r="AH14" s="39"/>
     </row>
     <row r="15">
-      <c r="A15" s="32"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -14468,8 +16441,8 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
       <c r="M15" s="39"/>
       <c r="N15" s="39"/>
       <c r="O15" s="39"/>
@@ -14494,7 +16467,7 @@
       <c r="AH15" s="39"/>
     </row>
     <row r="16">
-      <c r="A16" s="32"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -14504,8 +16477,8 @@
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
       <c r="M16" s="39"/>
       <c r="N16" s="39"/>
       <c r="O16" s="39"/>
@@ -14530,7 +16503,7 @@
       <c r="AH16" s="39"/>
     </row>
     <row r="17">
-      <c r="A17" s="32"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -14540,8 +16513,8 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
       <c r="M17" s="39"/>
       <c r="N17" s="39"/>
       <c r="O17" s="39"/>
@@ -14566,7 +16539,7 @@
       <c r="AH17" s="39"/>
     </row>
     <row r="18">
-      <c r="A18" s="32"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -14576,8 +16549,8 @@
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
       <c r="M18" s="39"/>
       <c r="N18" s="39"/>
       <c r="O18" s="39"/>
@@ -14602,7 +16575,7 @@
       <c r="AH18" s="39"/>
     </row>
     <row r="19">
-      <c r="A19" s="32"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
@@ -14612,8 +16585,8 @@
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="39"/>
       <c r="N19" s="39"/>
       <c r="O19" s="39"/>
@@ -14638,7 +16611,7 @@
       <c r="AH19" s="39"/>
     </row>
     <row r="20">
-      <c r="A20" s="32"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -14648,8 +16621,8 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
       <c r="M20" s="39"/>
       <c r="N20" s="39"/>
       <c r="O20" s="39"/>
@@ -14674,7 +16647,7 @@
       <c r="AH20" s="39"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="32"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -14684,8 +16657,8 @@
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
       <c r="M21" s="39"/>
       <c r="N21" s="39"/>
       <c r="O21" s="39"/>
@@ -14710,7 +16683,7 @@
       <c r="AH21" s="39"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="32"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -14720,8 +16693,8 @@
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
       <c r="M22" s="39"/>
       <c r="N22" s="39"/>
       <c r="O22" s="39"/>
@@ -14746,7 +16719,7 @@
       <c r="AH22" s="39"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="32"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -14756,8 +16729,8 @@
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
       <c r="M23" s="39"/>
       <c r="N23" s="39"/>
       <c r="O23" s="39"/>
@@ -14782,7 +16755,7 @@
       <c r="AH23" s="39"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="32"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -14792,8 +16765,8 @@
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
       <c r="M24" s="39"/>
       <c r="N24" s="39"/>
       <c r="O24" s="39"/>
@@ -14818,7 +16791,7 @@
       <c r="AH24" s="39"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="32"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -14828,8 +16801,8 @@
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
       <c r="M25" s="39"/>
       <c r="N25" s="39"/>
       <c r="O25" s="39"/>
@@ -14854,7 +16827,7 @@
       <c r="AH25" s="39"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="32"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -14864,8 +16837,8 @@
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
       <c r="M26" s="39"/>
       <c r="N26" s="39"/>
       <c r="O26" s="39"/>
@@ -14890,7 +16863,7 @@
       <c r="AH26" s="39"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="32"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -14900,8 +16873,8 @@
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
       <c r="M27" s="39"/>
       <c r="N27" s="39"/>
       <c r="O27" s="39"/>
@@ -14926,7 +16899,7 @@
       <c r="AH27" s="39"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="32"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
@@ -14936,8 +16909,8 @@
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
       <c r="M28" s="39"/>
       <c r="N28" s="39"/>
       <c r="O28" s="39"/>
@@ -14962,7 +16935,7 @@
       <c r="AH28" s="39"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="32"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
@@ -14972,8 +16945,8 @@
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="39"/>
       <c r="N29" s="39"/>
       <c r="O29" s="39"/>
@@ -14998,7 +16971,7 @@
       <c r="AH29" s="39"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="32"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
@@ -15008,8 +16981,8 @@
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="39"/>
       <c r="N30" s="39"/>
       <c r="O30" s="39"/>
@@ -15034,7 +17007,7 @@
       <c r="AH30" s="39"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="32"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
@@ -15044,8 +17017,8 @@
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="39"/>
       <c r="N31" s="39"/>
       <c r="O31" s="39"/>
@@ -15070,7 +17043,7 @@
       <c r="AH31" s="39"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="32"/>
+      <c r="A32" s="33"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -15080,8 +17053,8 @@
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
@@ -15106,7 +17079,7 @@
       <c r="AH32" s="39"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="32"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
@@ -15116,8 +17089,8 @@
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
       <c r="O33" s="39"/>
@@ -15142,7 +17115,7 @@
       <c r="AH33" s="39"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="32"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
@@ -15152,8 +17125,8 @@
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
       <c r="O34" s="39"/>
@@ -15178,7 +17151,7 @@
       <c r="AH34" s="39"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="32"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -15188,8 +17161,8 @@
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="39"/>
       <c r="N35" s="39"/>
       <c r="O35" s="39"/>
@@ -15214,7 +17187,7 @@
       <c r="AH35" s="39"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="32"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
@@ -15224,8 +17197,8 @@
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
       <c r="J36" s="14"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="39"/>
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
@@ -15250,7 +17223,7 @@
       <c r="AH36" s="39"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="32"/>
+      <c r="A37" s="33"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
@@ -15260,8 +17233,8 @@
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
       <c r="M37" s="39"/>
       <c r="N37" s="39"/>
       <c r="O37" s="39"/>
@@ -15286,7 +17259,7 @@
       <c r="AH37" s="39"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="32"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
@@ -15296,8 +17269,8 @@
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
       <c r="M38" s="39"/>
       <c r="N38" s="39"/>
       <c r="O38" s="39"/>
@@ -15322,7 +17295,7 @@
       <c r="AH38" s="39"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="32"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
@@ -15332,8 +17305,8 @@
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
       <c r="O39" s="39"/>
@@ -15358,7 +17331,7 @@
       <c r="AH39" s="39"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="32"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
@@ -15368,8 +17341,8 @@
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
@@ -15394,7 +17367,7 @@
       <c r="AH40" s="39"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="32"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
@@ -15404,8 +17377,8 @@
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
       <c r="M41" s="39"/>
       <c r="N41" s="39"/>
       <c r="O41" s="39"/>
@@ -15430,7 +17403,7 @@
       <c r="AH41" s="39"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="32"/>
+      <c r="A42" s="33"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
@@ -15440,8 +17413,8 @@
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
       <c r="M42" s="39"/>
       <c r="N42" s="39"/>
       <c r="O42" s="39"/>
@@ -15466,7 +17439,7 @@
       <c r="AH42" s="39"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="32"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -15476,8 +17449,8 @@
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
       <c r="M43" s="39"/>
       <c r="N43" s="39"/>
       <c r="O43" s="39"/>
@@ -15502,7 +17475,7 @@
       <c r="AH43" s="39"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="32"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -15512,8 +17485,8 @@
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
       <c r="M44" s="39"/>
       <c r="N44" s="39"/>
       <c r="O44" s="39"/>
@@ -15538,7 +17511,7 @@
       <c r="AH44" s="39"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="32"/>
+      <c r="A45" s="33"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
@@ -15548,8 +17521,8 @@
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
       <c r="M45" s="39"/>
       <c r="N45" s="39"/>
       <c r="O45" s="39"/>
@@ -15574,7 +17547,7 @@
       <c r="AH45" s="39"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="32"/>
+      <c r="A46" s="33"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
@@ -15584,8 +17557,8 @@
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
       <c r="M46" s="39"/>
       <c r="N46" s="39"/>
       <c r="O46" s="39"/>
@@ -15610,7 +17583,7 @@
       <c r="AH46" s="39"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="32"/>
+      <c r="A47" s="33"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
@@ -15620,8 +17593,8 @@
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
       <c r="M47" s="39"/>
       <c r="N47" s="39"/>
       <c r="O47" s="39"/>
@@ -15646,7 +17619,7 @@
       <c r="AH47" s="39"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="32"/>
+      <c r="A48" s="33"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
       <c r="D48" s="15"/>
@@ -15656,8 +17629,8 @@
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="14"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
       <c r="M48" s="39"/>
       <c r="N48" s="39"/>
       <c r="O48" s="39"/>
@@ -15682,7 +17655,7 @@
       <c r="AH48" s="39"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="32"/>
+      <c r="A49" s="33"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
@@ -15692,8 +17665,8 @@
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="14"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
       <c r="M49" s="39"/>
       <c r="N49" s="39"/>
       <c r="O49" s="39"/>
@@ -15718,7 +17691,7 @@
       <c r="AH49" s="39"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="32"/>
+      <c r="A50" s="33"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
@@ -15728,8 +17701,8 @@
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
       <c r="J50" s="14"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
       <c r="M50" s="39"/>
       <c r="N50" s="39"/>
       <c r="O50" s="39"/>
@@ -15754,7 +17727,7 @@
       <c r="AH50" s="39"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="32"/>
+      <c r="A51" s="33"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
       <c r="D51" s="15"/>
@@ -15764,8 +17737,8 @@
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
       <c r="M51" s="39"/>
       <c r="N51" s="39"/>
       <c r="O51" s="39"/>
@@ -15790,7 +17763,7 @@
       <c r="AH51" s="39"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="32"/>
+      <c r="A52" s="33"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -15800,8 +17773,8 @@
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
       <c r="M52" s="39"/>
       <c r="N52" s="39"/>
       <c r="O52" s="39"/>
@@ -15826,7 +17799,7 @@
       <c r="AH52" s="39"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="32"/>
+      <c r="A53" s="33"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
       <c r="D53" s="15"/>
@@ -15836,8 +17809,8 @@
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
       <c r="M53" s="39"/>
       <c r="N53" s="39"/>
       <c r="O53" s="39"/>
@@ -15862,7 +17835,7 @@
       <c r="AH53" s="39"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="32"/>
+      <c r="A54" s="33"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
       <c r="D54" s="15"/>
@@ -15872,8 +17845,8 @@
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
       <c r="M54" s="39"/>
       <c r="N54" s="39"/>
       <c r="O54" s="39"/>
@@ -15898,7 +17871,7 @@
       <c r="AH54" s="39"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="32"/>
+      <c r="A55" s="33"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
@@ -15908,8 +17881,8 @@
       <c r="H55" s="14"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="33"/>
       <c r="M55" s="39"/>
       <c r="N55" s="39"/>
       <c r="O55" s="39"/>
@@ -15934,7 +17907,7 @@
       <c r="AH55" s="39"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="32"/>
+      <c r="A56" s="33"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
@@ -15944,8 +17917,8 @@
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
       <c r="M56" s="39"/>
       <c r="N56" s="39"/>
       <c r="O56" s="39"/>
@@ -15970,7 +17943,7 @@
       <c r="AH56" s="39"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="32"/>
+      <c r="A57" s="33"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
       <c r="D57" s="15"/>
@@ -15980,8 +17953,8 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
       <c r="M57" s="39"/>
       <c r="N57" s="39"/>
       <c r="O57" s="39"/>
@@ -16006,7 +17979,7 @@
       <c r="AH57" s="39"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="32"/>
+      <c r="A58" s="33"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
       <c r="D58" s="15"/>
@@ -16016,8 +17989,8 @@
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
       <c r="M58" s="39"/>
       <c r="N58" s="39"/>
       <c r="O58" s="39"/>
@@ -16042,7 +18015,7 @@
       <c r="AH58" s="39"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="32"/>
+      <c r="A59" s="33"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
       <c r="D59" s="15"/>
@@ -16052,8 +18025,8 @@
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
       <c r="M59" s="39"/>
       <c r="N59" s="39"/>
       <c r="O59" s="39"/>
@@ -16078,7 +18051,7 @@
       <c r="AH59" s="39"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="32"/>
+      <c r="A60" s="33"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
@@ -16088,8 +18061,8 @@
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
       <c r="M60" s="39"/>
       <c r="N60" s="39"/>
       <c r="O60" s="39"/>
@@ -16114,7 +18087,7 @@
       <c r="AH60" s="39"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="32"/>
+      <c r="A61" s="33"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="15"/>
@@ -16124,8 +18097,8 @@
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
       <c r="M61" s="39"/>
       <c r="N61" s="39"/>
       <c r="O61" s="39"/>
@@ -16150,7 +18123,7 @@
       <c r="AH61" s="39"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="32"/>
+      <c r="A62" s="33"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
       <c r="D62" s="15"/>
@@ -16160,8 +18133,8 @@
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
       <c r="M62" s="39"/>
       <c r="N62" s="39"/>
       <c r="O62" s="39"/>
@@ -16186,7 +18159,7 @@
       <c r="AH62" s="39"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="32"/>
+      <c r="A63" s="33"/>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
       <c r="D63" s="15"/>
@@ -16196,8 +18169,8 @@
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
       <c r="M63" s="39"/>
       <c r="N63" s="39"/>
       <c r="O63" s="39"/>
@@ -16222,7 +18195,7 @@
       <c r="AH63" s="39"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="32"/>
+      <c r="A64" s="33"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
       <c r="D64" s="15"/>
@@ -16232,8 +18205,8 @@
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
       <c r="M64" s="39"/>
       <c r="N64" s="39"/>
       <c r="O64" s="39"/>
@@ -16258,7 +18231,7 @@
       <c r="AH64" s="39"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="32"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
       <c r="D65" s="15"/>
@@ -16268,8 +18241,8 @@
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="32"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
       <c r="M65" s="39"/>
       <c r="N65" s="39"/>
       <c r="O65" s="39"/>
@@ -16294,7 +18267,7 @@
       <c r="AH65" s="39"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="32"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
@@ -16304,8 +18277,8 @@
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
       <c r="M66" s="39"/>
       <c r="N66" s="39"/>
       <c r="O66" s="39"/>
@@ -16330,7 +18303,7 @@
       <c r="AH66" s="39"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="32"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
       <c r="D67" s="15"/>
@@ -16340,8 +18313,8 @@
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="33"/>
       <c r="M67" s="39"/>
       <c r="N67" s="39"/>
       <c r="O67" s="39"/>
@@ -16366,7 +18339,7 @@
       <c r="AH67" s="39"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="32"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
@@ -16376,8 +18349,8 @@
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
       <c r="J68" s="14"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
       <c r="M68" s="39"/>
       <c r="N68" s="39"/>
       <c r="O68" s="39"/>
@@ -16402,7 +18375,7 @@
       <c r="AH68" s="39"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="32"/>
+      <c r="A69" s="33"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -16412,8 +18385,8 @@
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
       <c r="M69" s="39"/>
       <c r="N69" s="39"/>
       <c r="O69" s="39"/>
@@ -16438,7 +18411,7 @@
       <c r="AH69" s="39"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="32"/>
+      <c r="A70" s="33"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -16448,8 +18421,8 @@
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
       <c r="M70" s="39"/>
       <c r="N70" s="39"/>
       <c r="O70" s="39"/>
@@ -16474,7 +18447,7 @@
       <c r="AH70" s="39"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="32"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
@@ -16484,8 +18457,8 @@
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
       <c r="M71" s="39"/>
       <c r="N71" s="39"/>
       <c r="O71" s="39"/>
@@ -16510,7 +18483,7 @@
       <c r="AH71" s="39"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="32"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
@@ -16520,8 +18493,8 @@
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
+      <c r="K72" s="33"/>
+      <c r="L72" s="33"/>
       <c r="M72" s="39"/>
       <c r="N72" s="39"/>
       <c r="O72" s="39"/>
@@ -16546,7 +18519,7 @@
       <c r="AH72" s="39"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="32"/>
+      <c r="A73" s="33"/>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
@@ -16556,8 +18529,8 @@
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
+      <c r="K73" s="33"/>
+      <c r="L73" s="33"/>
       <c r="M73" s="39"/>
       <c r="N73" s="39"/>
       <c r="O73" s="39"/>
@@ -16582,7 +18555,7 @@
       <c r="AH73" s="39"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="32"/>
+      <c r="A74" s="33"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
@@ -16592,8 +18565,8 @@
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
+      <c r="K74" s="33"/>
+      <c r="L74" s="33"/>
       <c r="M74" s="39"/>
       <c r="N74" s="39"/>
       <c r="O74" s="39"/>
@@ -16618,7 +18591,7 @@
       <c r="AH74" s="39"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="32"/>
+      <c r="A75" s="33"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
       <c r="D75" s="15"/>
@@ -16628,8 +18601,8 @@
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
-      <c r="K75" s="32"/>
-      <c r="L75" s="32"/>
+      <c r="K75" s="33"/>
+      <c r="L75" s="33"/>
       <c r="M75" s="39"/>
       <c r="N75" s="39"/>
       <c r="O75" s="39"/>
@@ -16654,7 +18627,7 @@
       <c r="AH75" s="39"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="32"/>
+      <c r="A76" s="33"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
       <c r="D76" s="15"/>
@@ -16664,8 +18637,8 @@
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
-      <c r="K76" s="32"/>
-      <c r="L76" s="32"/>
+      <c r="K76" s="33"/>
+      <c r="L76" s="33"/>
       <c r="M76" s="39"/>
       <c r="N76" s="39"/>
       <c r="O76" s="39"/>
@@ -16690,7 +18663,7 @@
       <c r="AH76" s="39"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="32"/>
+      <c r="A77" s="33"/>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
@@ -16700,8 +18673,8 @@
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="32"/>
+      <c r="K77" s="33"/>
+      <c r="L77" s="33"/>
       <c r="M77" s="39"/>
       <c r="N77" s="39"/>
       <c r="O77" s="39"/>
@@ -16726,7 +18699,7 @@
       <c r="AH77" s="39"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="32"/>
+      <c r="A78" s="33"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
       <c r="D78" s="15"/>
@@ -16736,8 +18709,8 @@
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14"/>
-      <c r="K78" s="32"/>
-      <c r="L78" s="32"/>
+      <c r="K78" s="33"/>
+      <c r="L78" s="33"/>
       <c r="M78" s="39"/>
       <c r="N78" s="39"/>
       <c r="O78" s="39"/>
@@ -16762,7 +18735,7 @@
       <c r="AH78" s="39"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="32"/>
+      <c r="A79" s="33"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
       <c r="D79" s="15"/>
@@ -16772,8 +18745,8 @@
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14"/>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
+      <c r="K79" s="33"/>
+      <c r="L79" s="33"/>
       <c r="M79" s="39"/>
       <c r="N79" s="39"/>
       <c r="O79" s="39"/>
@@ -16798,7 +18771,7 @@
       <c r="AH79" s="39"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="32"/>
+      <c r="A80" s="33"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
@@ -16808,8 +18781,8 @@
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
-      <c r="K80" s="32"/>
-      <c r="L80" s="32"/>
+      <c r="K80" s="33"/>
+      <c r="L80" s="33"/>
       <c r="M80" s="39"/>
       <c r="N80" s="39"/>
       <c r="O80" s="39"/>
@@ -16834,7 +18807,7 @@
       <c r="AH80" s="39"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="32"/>
+      <c r="A81" s="33"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" s="15"/>
@@ -16844,8 +18817,8 @@
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="14"/>
-      <c r="K81" s="32"/>
-      <c r="L81" s="32"/>
+      <c r="K81" s="33"/>
+      <c r="L81" s="33"/>
       <c r="M81" s="39"/>
       <c r="N81" s="39"/>
       <c r="O81" s="39"/>
@@ -16870,7 +18843,7 @@
       <c r="AH81" s="39"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="32"/>
+      <c r="A82" s="33"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
       <c r="D82" s="15"/>
@@ -16880,8 +18853,8 @@
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="14"/>
-      <c r="K82" s="32"/>
-      <c r="L82" s="32"/>
+      <c r="K82" s="33"/>
+      <c r="L82" s="33"/>
       <c r="M82" s="39"/>
       <c r="N82" s="39"/>
       <c r="O82" s="39"/>
@@ -16906,7 +18879,7 @@
       <c r="AH82" s="39"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="32"/>
+      <c r="A83" s="33"/>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
@@ -16916,8 +18889,8 @@
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
-      <c r="K83" s="32"/>
-      <c r="L83" s="32"/>
+      <c r="K83" s="33"/>
+      <c r="L83" s="33"/>
       <c r="M83" s="39"/>
       <c r="N83" s="39"/>
       <c r="O83" s="39"/>
@@ -16942,7 +18915,7 @@
       <c r="AH83" s="39"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="32"/>
+      <c r="A84" s="33"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
       <c r="D84" s="15"/>
@@ -16952,8 +18925,8 @@
       <c r="H84" s="14"/>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
-      <c r="K84" s="32"/>
-      <c r="L84" s="32"/>
+      <c r="K84" s="33"/>
+      <c r="L84" s="33"/>
       <c r="M84" s="39"/>
       <c r="N84" s="39"/>
       <c r="O84" s="39"/>
@@ -16978,7 +18951,7 @@
       <c r="AH84" s="39"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="32"/>
+      <c r="A85" s="33"/>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
       <c r="D85" s="15"/>
@@ -16988,8 +18961,8 @@
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
-      <c r="K85" s="32"/>
-      <c r="L85" s="32"/>
+      <c r="K85" s="33"/>
+      <c r="L85" s="33"/>
       <c r="M85" s="39"/>
       <c r="N85" s="39"/>
       <c r="O85" s="39"/>
@@ -17014,7 +18987,7 @@
       <c r="AH85" s="39"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="32"/>
+      <c r="A86" s="33"/>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
@@ -17024,8 +18997,8 @@
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
+      <c r="K86" s="33"/>
+      <c r="L86" s="33"/>
       <c r="M86" s="39"/>
       <c r="N86" s="39"/>
       <c r="O86" s="39"/>
@@ -17050,7 +19023,7 @@
       <c r="AH86" s="39"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="32"/>
+      <c r="A87" s="33"/>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
       <c r="D87" s="15"/>
@@ -17060,8 +19033,8 @@
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="14"/>
-      <c r="K87" s="32"/>
-      <c r="L87" s="32"/>
+      <c r="K87" s="33"/>
+      <c r="L87" s="33"/>
       <c r="M87" s="39"/>
       <c r="N87" s="39"/>
       <c r="O87" s="39"/>
@@ -17086,7 +19059,7 @@
       <c r="AH87" s="39"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="32"/>
+      <c r="A88" s="33"/>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
       <c r="D88" s="15"/>
@@ -17096,8 +19069,8 @@
       <c r="H88" s="14"/>
       <c r="I88" s="14"/>
       <c r="J88" s="14"/>
-      <c r="K88" s="32"/>
-      <c r="L88" s="32"/>
+      <c r="K88" s="33"/>
+      <c r="L88" s="33"/>
       <c r="M88" s="39"/>
       <c r="N88" s="39"/>
       <c r="O88" s="39"/>
@@ -17122,7 +19095,7 @@
       <c r="AH88" s="39"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="32"/>
+      <c r="A89" s="33"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
       <c r="D89" s="15"/>
@@ -17132,8 +19105,8 @@
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
       <c r="J89" s="14"/>
-      <c r="K89" s="32"/>
-      <c r="L89" s="32"/>
+      <c r="K89" s="33"/>
+      <c r="L89" s="33"/>
       <c r="M89" s="39"/>
       <c r="N89" s="39"/>
       <c r="O89" s="39"/>
@@ -17158,7 +19131,7 @@
       <c r="AH89" s="39"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="32"/>
+      <c r="A90" s="33"/>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
       <c r="D90" s="15"/>
@@ -17168,8 +19141,8 @@
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
-      <c r="K90" s="32"/>
-      <c r="L90" s="32"/>
+      <c r="K90" s="33"/>
+      <c r="L90" s="33"/>
       <c r="M90" s="39"/>
       <c r="N90" s="39"/>
       <c r="O90" s="39"/>
@@ -17194,7 +19167,7 @@
       <c r="AH90" s="39"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="32"/>
+      <c r="A91" s="33"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
       <c r="D91" s="15"/>
@@ -17204,8 +19177,8 @@
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
-      <c r="K91" s="32"/>
-      <c r="L91" s="32"/>
+      <c r="K91" s="33"/>
+      <c r="L91" s="33"/>
       <c r="M91" s="39"/>
       <c r="N91" s="39"/>
       <c r="O91" s="39"/>
@@ -17230,7 +19203,7 @@
       <c r="AH91" s="39"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="32"/>
+      <c r="A92" s="33"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
       <c r="D92" s="15"/>
@@ -17240,8 +19213,8 @@
       <c r="H92" s="14"/>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
-      <c r="K92" s="32"/>
-      <c r="L92" s="32"/>
+      <c r="K92" s="33"/>
+      <c r="L92" s="33"/>
       <c r="M92" s="39"/>
       <c r="N92" s="39"/>
       <c r="O92" s="39"/>
@@ -17266,7 +19239,7 @@
       <c r="AH92" s="39"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="32"/>
+      <c r="A93" s="33"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
       <c r="D93" s="15"/>
@@ -17276,8 +19249,8 @@
       <c r="H93" s="14"/>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
-      <c r="K93" s="32"/>
-      <c r="L93" s="32"/>
+      <c r="K93" s="33"/>
+      <c r="L93" s="33"/>
       <c r="M93" s="39"/>
       <c r="N93" s="39"/>
       <c r="O93" s="39"/>
@@ -17302,7 +19275,7 @@
       <c r="AH93" s="39"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="32"/>
+      <c r="A94" s="33"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
       <c r="D94" s="15"/>
@@ -17312,8 +19285,8 @@
       <c r="H94" s="14"/>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
-      <c r="K94" s="32"/>
-      <c r="L94" s="32"/>
+      <c r="K94" s="33"/>
+      <c r="L94" s="33"/>
       <c r="M94" s="39"/>
       <c r="N94" s="39"/>
       <c r="O94" s="39"/>
@@ -17338,7 +19311,7 @@
       <c r="AH94" s="39"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="32"/>
+      <c r="A95" s="33"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
       <c r="D95" s="15"/>
@@ -17348,8 +19321,8 @@
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
-      <c r="K95" s="32"/>
-      <c r="L95" s="32"/>
+      <c r="K95" s="33"/>
+      <c r="L95" s="33"/>
       <c r="M95" s="39"/>
       <c r="N95" s="39"/>
       <c r="O95" s="39"/>
@@ -17374,7 +19347,7 @@
       <c r="AH95" s="39"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="32"/>
+      <c r="A96" s="33"/>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
       <c r="D96" s="15"/>
@@ -17384,8 +19357,8 @@
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
-      <c r="K96" s="32"/>
-      <c r="L96" s="32"/>
+      <c r="K96" s="33"/>
+      <c r="L96" s="33"/>
       <c r="M96" s="39"/>
       <c r="N96" s="39"/>
       <c r="O96" s="39"/>
@@ -17410,7 +19383,7 @@
       <c r="AH96" s="39"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="32"/>
+      <c r="A97" s="33"/>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
@@ -17420,8 +19393,8 @@
       <c r="H97" s="14"/>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
-      <c r="K97" s="32"/>
-      <c r="L97" s="32"/>
+      <c r="K97" s="33"/>
+      <c r="L97" s="33"/>
       <c r="M97" s="39"/>
       <c r="N97" s="39"/>
       <c r="O97" s="39"/>
@@ -17446,7 +19419,7 @@
       <c r="AH97" s="39"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="32"/>
+      <c r="A98" s="33"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
       <c r="D98" s="15"/>
@@ -17456,8 +19429,8 @@
       <c r="H98" s="14"/>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
-      <c r="K98" s="32"/>
-      <c r="L98" s="32"/>
+      <c r="K98" s="33"/>
+      <c r="L98" s="33"/>
       <c r="M98" s="39"/>
       <c r="N98" s="39"/>
       <c r="O98" s="39"/>
@@ -17482,7 +19455,7 @@
       <c r="AH98" s="39"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="32"/>
+      <c r="A99" s="33"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="15"/>
@@ -17492,8 +19465,8 @@
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
       <c r="J99" s="14"/>
-      <c r="K99" s="32"/>
-      <c r="L99" s="32"/>
+      <c r="K99" s="33"/>
+      <c r="L99" s="33"/>
       <c r="M99" s="39"/>
       <c r="N99" s="39"/>
       <c r="O99" s="39"/>
@@ -17518,7 +19491,7 @@
       <c r="AH99" s="39"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="32"/>
+      <c r="A100" s="33"/>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
       <c r="D100" s="15"/>
@@ -17528,8 +19501,8 @@
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
-      <c r="K100" s="32"/>
-      <c r="L100" s="32"/>
+      <c r="K100" s="33"/>
+      <c r="L100" s="33"/>
       <c r="M100" s="39"/>
       <c r="N100" s="39"/>
       <c r="O100" s="39"/>
@@ -17554,7 +19527,7 @@
       <c r="AH100" s="39"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="32"/>
+      <c r="A101" s="33"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
       <c r="D101" s="15"/>
@@ -17564,8 +19537,8 @@
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
-      <c r="K101" s="32"/>
-      <c r="L101" s="32"/>
+      <c r="K101" s="33"/>
+      <c r="L101" s="33"/>
       <c r="M101" s="39"/>
       <c r="N101" s="39"/>
       <c r="O101" s="39"/>
@@ -17590,7 +19563,7 @@
       <c r="AH101" s="39"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="32"/>
+      <c r="A102" s="33"/>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
       <c r="D102" s="15"/>
@@ -17600,8 +19573,8 @@
       <c r="H102" s="14"/>
       <c r="I102" s="14"/>
       <c r="J102" s="14"/>
-      <c r="K102" s="32"/>
-      <c r="L102" s="32"/>
+      <c r="K102" s="33"/>
+      <c r="L102" s="33"/>
       <c r="M102" s="39"/>
       <c r="N102" s="39"/>
       <c r="O102" s="39"/>
@@ -17626,7 +19599,7 @@
       <c r="AH102" s="39"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="32"/>
+      <c r="A103" s="33"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
       <c r="D103" s="15"/>
@@ -17636,8 +19609,8 @@
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
       <c r="J103" s="14"/>
-      <c r="K103" s="32"/>
-      <c r="L103" s="32"/>
+      <c r="K103" s="33"/>
+      <c r="L103" s="33"/>
       <c r="M103" s="39"/>
       <c r="N103" s="39"/>
       <c r="O103" s="39"/>
@@ -17662,7 +19635,7 @@
       <c r="AH103" s="39"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="32"/>
+      <c r="A104" s="33"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
       <c r="D104" s="15"/>
@@ -17672,8 +19645,8 @@
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="14"/>
-      <c r="K104" s="32"/>
-      <c r="L104" s="32"/>
+      <c r="K104" s="33"/>
+      <c r="L104" s="33"/>
       <c r="M104" s="39"/>
       <c r="N104" s="39"/>
       <c r="O104" s="39"/>
@@ -17698,7 +19671,7 @@
       <c r="AH104" s="39"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="32"/>
+      <c r="A105" s="33"/>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
       <c r="D105" s="15"/>
@@ -17708,8 +19681,8 @@
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
-      <c r="K105" s="32"/>
-      <c r="L105" s="32"/>
+      <c r="K105" s="33"/>
+      <c r="L105" s="33"/>
       <c r="M105" s="39"/>
       <c r="N105" s="39"/>
       <c r="O105" s="39"/>
@@ -17734,7 +19707,7 @@
       <c r="AH105" s="39"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="32"/>
+      <c r="A106" s="33"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
       <c r="D106" s="15"/>
@@ -17744,8 +19717,8 @@
       <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="14"/>
-      <c r="K106" s="32"/>
-      <c r="L106" s="32"/>
+      <c r="K106" s="33"/>
+      <c r="L106" s="33"/>
       <c r="M106" s="39"/>
       <c r="N106" s="39"/>
       <c r="O106" s="39"/>
@@ -17770,7 +19743,7 @@
       <c r="AH106" s="39"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="32"/>
+      <c r="A107" s="33"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
       <c r="D107" s="15"/>
@@ -17780,8 +19753,8 @@
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
-      <c r="K107" s="32"/>
-      <c r="L107" s="32"/>
+      <c r="K107" s="33"/>
+      <c r="L107" s="33"/>
       <c r="M107" s="39"/>
       <c r="N107" s="39"/>
       <c r="O107" s="39"/>
@@ -17806,7 +19779,7 @@
       <c r="AH107" s="39"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="32"/>
+      <c r="A108" s="33"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
       <c r="D108" s="15"/>
@@ -17816,8 +19789,8 @@
       <c r="H108" s="14"/>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
-      <c r="K108" s="32"/>
-      <c r="L108" s="32"/>
+      <c r="K108" s="33"/>
+      <c r="L108" s="33"/>
       <c r="M108" s="39"/>
       <c r="N108" s="39"/>
       <c r="O108" s="39"/>
@@ -17842,7 +19815,7 @@
       <c r="AH108" s="39"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="32"/>
+      <c r="A109" s="33"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
       <c r="D109" s="15"/>
@@ -17852,8 +19825,8 @@
       <c r="H109" s="14"/>
       <c r="I109" s="14"/>
       <c r="J109" s="14"/>
-      <c r="K109" s="32"/>
-      <c r="L109" s="32"/>
+      <c r="K109" s="33"/>
+      <c r="L109" s="33"/>
       <c r="M109" s="39"/>
       <c r="N109" s="39"/>
       <c r="O109" s="39"/>
@@ -17878,7 +19851,7 @@
       <c r="AH109" s="39"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="32"/>
+      <c r="A110" s="33"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
       <c r="D110" s="15"/>
@@ -17888,8 +19861,8 @@
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="14"/>
-      <c r="K110" s="32"/>
-      <c r="L110" s="32"/>
+      <c r="K110" s="33"/>
+      <c r="L110" s="33"/>
       <c r="M110" s="39"/>
       <c r="N110" s="39"/>
       <c r="O110" s="39"/>
@@ -17914,7 +19887,7 @@
       <c r="AH110" s="39"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="32"/>
+      <c r="A111" s="33"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
@@ -17924,8 +19897,8 @@
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="14"/>
-      <c r="K111" s="32"/>
-      <c r="L111" s="32"/>
+      <c r="K111" s="33"/>
+      <c r="L111" s="33"/>
       <c r="M111" s="39"/>
       <c r="N111" s="39"/>
       <c r="O111" s="39"/>
@@ -17950,7 +19923,7 @@
       <c r="AH111" s="39"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="32"/>
+      <c r="A112" s="33"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
       <c r="D112" s="15"/>
@@ -17960,8 +19933,8 @@
       <c r="H112" s="14"/>
       <c r="I112" s="14"/>
       <c r="J112" s="14"/>
-      <c r="K112" s="32"/>
-      <c r="L112" s="32"/>
+      <c r="K112" s="33"/>
+      <c r="L112" s="33"/>
       <c r="M112" s="39"/>
       <c r="N112" s="39"/>
       <c r="O112" s="39"/>
@@ -17986,7 +19959,7 @@
       <c r="AH112" s="39"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="32"/>
+      <c r="A113" s="33"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
       <c r="D113" s="15"/>
@@ -17996,8 +19969,8 @@
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="14"/>
-      <c r="K113" s="32"/>
-      <c r="L113" s="32"/>
+      <c r="K113" s="33"/>
+      <c r="L113" s="33"/>
       <c r="M113" s="39"/>
       <c r="N113" s="39"/>
       <c r="O113" s="39"/>
@@ -18022,7 +19995,7 @@
       <c r="AH113" s="39"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="32"/>
+      <c r="A114" s="33"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
       <c r="D114" s="15"/>
@@ -18032,8 +20005,8 @@
       <c r="H114" s="14"/>
       <c r="I114" s="14"/>
       <c r="J114" s="14"/>
-      <c r="K114" s="32"/>
-      <c r="L114" s="32"/>
+      <c r="K114" s="33"/>
+      <c r="L114" s="33"/>
       <c r="M114" s="39"/>
       <c r="N114" s="39"/>
       <c r="O114" s="39"/>
@@ -18058,7 +20031,7 @@
       <c r="AH114" s="39"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="32"/>
+      <c r="A115" s="33"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
       <c r="D115" s="15"/>
@@ -18068,8 +20041,8 @@
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="14"/>
-      <c r="K115" s="32"/>
-      <c r="L115" s="32"/>
+      <c r="K115" s="33"/>
+      <c r="L115" s="33"/>
       <c r="M115" s="39"/>
       <c r="N115" s="39"/>
       <c r="O115" s="39"/>
@@ -18094,7 +20067,7 @@
       <c r="AH115" s="39"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="32"/>
+      <c r="A116" s="33"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
       <c r="D116" s="15"/>
@@ -18104,8 +20077,8 @@
       <c r="H116" s="14"/>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
-      <c r="K116" s="32"/>
-      <c r="L116" s="32"/>
+      <c r="K116" s="33"/>
+      <c r="L116" s="33"/>
       <c r="M116" s="39"/>
       <c r="N116" s="39"/>
       <c r="O116" s="39"/>
@@ -18130,7 +20103,7 @@
       <c r="AH116" s="39"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="32"/>
+      <c r="A117" s="33"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
       <c r="D117" s="15"/>
@@ -18140,8 +20113,8 @@
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
-      <c r="K117" s="32"/>
-      <c r="L117" s="32"/>
+      <c r="K117" s="33"/>
+      <c r="L117" s="33"/>
       <c r="M117" s="39"/>
       <c r="N117" s="39"/>
       <c r="O117" s="39"/>
@@ -18166,7 +20139,7 @@
       <c r="AH117" s="39"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="32"/>
+      <c r="A118" s="33"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
       <c r="D118" s="15"/>
@@ -18176,8 +20149,8 @@
       <c r="H118" s="14"/>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
-      <c r="K118" s="32"/>
-      <c r="L118" s="32"/>
+      <c r="K118" s="33"/>
+      <c r="L118" s="33"/>
       <c r="M118" s="39"/>
       <c r="N118" s="39"/>
       <c r="O118" s="39"/>
@@ -18202,7 +20175,7 @@
       <c r="AH118" s="39"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="32"/>
+      <c r="A119" s="33"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
       <c r="D119" s="15"/>
@@ -18212,8 +20185,8 @@
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="14"/>
-      <c r="K119" s="32"/>
-      <c r="L119" s="32"/>
+      <c r="K119" s="33"/>
+      <c r="L119" s="33"/>
       <c r="M119" s="39"/>
       <c r="N119" s="39"/>
       <c r="O119" s="39"/>
@@ -18238,7 +20211,7 @@
       <c r="AH119" s="39"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="32"/>
+      <c r="A120" s="33"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
       <c r="D120" s="15"/>
@@ -18248,8 +20221,8 @@
       <c r="H120" s="14"/>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
-      <c r="K120" s="32"/>
-      <c r="L120" s="32"/>
+      <c r="K120" s="33"/>
+      <c r="L120" s="33"/>
       <c r="M120" s="39"/>
       <c r="N120" s="39"/>
       <c r="O120" s="39"/>
@@ -18274,7 +20247,7 @@
       <c r="AH120" s="39"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="32"/>
+      <c r="A121" s="33"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
       <c r="D121" s="15"/>
@@ -18284,8 +20257,8 @@
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
       <c r="J121" s="14"/>
-      <c r="K121" s="32"/>
-      <c r="L121" s="32"/>
+      <c r="K121" s="33"/>
+      <c r="L121" s="33"/>
       <c r="M121" s="39"/>
       <c r="N121" s="39"/>
       <c r="O121" s="39"/>
@@ -18310,7 +20283,7 @@
       <c r="AH121" s="39"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="32"/>
+      <c r="A122" s="33"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
       <c r="D122" s="15"/>
@@ -18320,8 +20293,8 @@
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
       <c r="J122" s="14"/>
-      <c r="K122" s="32"/>
-      <c r="L122" s="32"/>
+      <c r="K122" s="33"/>
+      <c r="L122" s="33"/>
       <c r="M122" s="39"/>
       <c r="N122" s="39"/>
       <c r="O122" s="39"/>
@@ -18346,7 +20319,7 @@
       <c r="AH122" s="39"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="32"/>
+      <c r="A123" s="33"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
       <c r="D123" s="15"/>
@@ -18356,8 +20329,8 @@
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
-      <c r="K123" s="32"/>
-      <c r="L123" s="32"/>
+      <c r="K123" s="33"/>
+      <c r="L123" s="33"/>
       <c r="M123" s="39"/>
       <c r="N123" s="39"/>
       <c r="O123" s="39"/>
@@ -18382,7 +20355,7 @@
       <c r="AH123" s="39"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="32"/>
+      <c r="A124" s="33"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
       <c r="D124" s="15"/>
@@ -18392,8 +20365,8 @@
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
-      <c r="K124" s="32"/>
-      <c r="L124" s="32"/>
+      <c r="K124" s="33"/>
+      <c r="L124" s="33"/>
       <c r="M124" s="39"/>
       <c r="N124" s="39"/>
       <c r="O124" s="39"/>
@@ -18418,7 +20391,7 @@
       <c r="AH124" s="39"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="32"/>
+      <c r="A125" s="33"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
       <c r="D125" s="15"/>
@@ -18428,8 +20401,8 @@
       <c r="H125" s="14"/>
       <c r="I125" s="14"/>
       <c r="J125" s="14"/>
-      <c r="K125" s="32"/>
-      <c r="L125" s="32"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="33"/>
       <c r="M125" s="39"/>
       <c r="N125" s="39"/>
       <c r="O125" s="39"/>
@@ -18454,7 +20427,7 @@
       <c r="AH125" s="39"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="32"/>
+      <c r="A126" s="33"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
       <c r="D126" s="15"/>
@@ -18464,8 +20437,8 @@
       <c r="H126" s="14"/>
       <c r="I126" s="14"/>
       <c r="J126" s="14"/>
-      <c r="K126" s="32"/>
-      <c r="L126" s="32"/>
+      <c r="K126" s="33"/>
+      <c r="L126" s="33"/>
       <c r="M126" s="39"/>
       <c r="N126" s="39"/>
       <c r="O126" s="39"/>
@@ -18490,7 +20463,7 @@
       <c r="AH126" s="39"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="32"/>
+      <c r="A127" s="33"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
       <c r="D127" s="15"/>
@@ -18500,8 +20473,8 @@
       <c r="H127" s="14"/>
       <c r="I127" s="14"/>
       <c r="J127" s="14"/>
-      <c r="K127" s="32"/>
-      <c r="L127" s="32"/>
+      <c r="K127" s="33"/>
+      <c r="L127" s="33"/>
       <c r="M127" s="39"/>
       <c r="N127" s="39"/>
       <c r="O127" s="39"/>
@@ -18526,7 +20499,7 @@
       <c r="AH127" s="39"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="32"/>
+      <c r="A128" s="33"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
       <c r="D128" s="15"/>
@@ -18536,8 +20509,8 @@
       <c r="H128" s="14"/>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
-      <c r="K128" s="32"/>
-      <c r="L128" s="32"/>
+      <c r="K128" s="33"/>
+      <c r="L128" s="33"/>
       <c r="M128" s="39"/>
       <c r="N128" s="39"/>
       <c r="O128" s="39"/>
@@ -18562,7 +20535,7 @@
       <c r="AH128" s="39"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="32"/>
+      <c r="A129" s="33"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
       <c r="D129" s="15"/>
@@ -18572,8 +20545,8 @@
       <c r="H129" s="14"/>
       <c r="I129" s="14"/>
       <c r="J129" s="14"/>
-      <c r="K129" s="32"/>
-      <c r="L129" s="32"/>
+      <c r="K129" s="33"/>
+      <c r="L129" s="33"/>
       <c r="M129" s="39"/>
       <c r="N129" s="39"/>
       <c r="O129" s="39"/>
@@ -18598,7 +20571,7 @@
       <c r="AH129" s="39"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="32"/>
+      <c r="A130" s="33"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
       <c r="D130" s="15"/>
@@ -18608,8 +20581,8 @@
       <c r="H130" s="14"/>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
-      <c r="K130" s="32"/>
-      <c r="L130" s="32"/>
+      <c r="K130" s="33"/>
+      <c r="L130" s="33"/>
       <c r="M130" s="39"/>
       <c r="N130" s="39"/>
       <c r="O130" s="39"/>
@@ -18634,7 +20607,7 @@
       <c r="AH130" s="39"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="32"/>
+      <c r="A131" s="33"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
       <c r="D131" s="15"/>
@@ -18644,8 +20617,8 @@
       <c r="H131" s="14"/>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
-      <c r="K131" s="32"/>
-      <c r="L131" s="32"/>
+      <c r="K131" s="33"/>
+      <c r="L131" s="33"/>
       <c r="M131" s="39"/>
       <c r="N131" s="39"/>
       <c r="O131" s="39"/>
@@ -18670,7 +20643,7 @@
       <c r="AH131" s="39"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="32"/>
+      <c r="A132" s="33"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
       <c r="D132" s="15"/>
@@ -18680,8 +20653,8 @@
       <c r="H132" s="14"/>
       <c r="I132" s="14"/>
       <c r="J132" s="14"/>
-      <c r="K132" s="32"/>
-      <c r="L132" s="32"/>
+      <c r="K132" s="33"/>
+      <c r="L132" s="33"/>
       <c r="M132" s="39"/>
       <c r="N132" s="39"/>
       <c r="O132" s="39"/>
@@ -18706,7 +20679,7 @@
       <c r="AH132" s="39"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="32"/>
+      <c r="A133" s="33"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
       <c r="D133" s="15"/>
@@ -18716,8 +20689,8 @@
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
       <c r="J133" s="14"/>
-      <c r="K133" s="32"/>
-      <c r="L133" s="32"/>
+      <c r="K133" s="33"/>
+      <c r="L133" s="33"/>
       <c r="M133" s="39"/>
       <c r="N133" s="39"/>
       <c r="O133" s="39"/>
@@ -18742,7 +20715,7 @@
       <c r="AH133" s="39"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="32"/>
+      <c r="A134" s="33"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
       <c r="D134" s="15"/>
@@ -18752,8 +20725,8 @@
       <c r="H134" s="14"/>
       <c r="I134" s="14"/>
       <c r="J134" s="14"/>
-      <c r="K134" s="32"/>
-      <c r="L134" s="32"/>
+      <c r="K134" s="33"/>
+      <c r="L134" s="33"/>
       <c r="M134" s="39"/>
       <c r="N134" s="39"/>
       <c r="O134" s="39"/>
@@ -18778,7 +20751,7 @@
       <c r="AH134" s="39"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="32"/>
+      <c r="A135" s="33"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
       <c r="D135" s="15"/>
@@ -18788,8 +20761,8 @@
       <c r="H135" s="14"/>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
-      <c r="K135" s="32"/>
-      <c r="L135" s="32"/>
+      <c r="K135" s="33"/>
+      <c r="L135" s="33"/>
       <c r="M135" s="39"/>
       <c r="N135" s="39"/>
       <c r="O135" s="39"/>
@@ -18814,7 +20787,7 @@
       <c r="AH135" s="39"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="32"/>
+      <c r="A136" s="33"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
       <c r="D136" s="15"/>
@@ -18824,8 +20797,8 @@
       <c r="H136" s="14"/>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
-      <c r="K136" s="32"/>
-      <c r="L136" s="32"/>
+      <c r="K136" s="33"/>
+      <c r="L136" s="33"/>
       <c r="M136" s="39"/>
       <c r="N136" s="39"/>
       <c r="O136" s="39"/>
@@ -18850,7 +20823,7 @@
       <c r="AH136" s="39"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="32"/>
+      <c r="A137" s="33"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
       <c r="D137" s="15"/>
@@ -18860,8 +20833,8 @@
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="14"/>
-      <c r="K137" s="32"/>
-      <c r="L137" s="32"/>
+      <c r="K137" s="33"/>
+      <c r="L137" s="33"/>
       <c r="M137" s="39"/>
       <c r="N137" s="39"/>
       <c r="O137" s="39"/>
@@ -18886,7 +20859,7 @@
       <c r="AH137" s="39"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="32"/>
+      <c r="A138" s="33"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
       <c r="D138" s="15"/>
@@ -18896,8 +20869,8 @@
       <c r="H138" s="14"/>
       <c r="I138" s="14"/>
       <c r="J138" s="14"/>
-      <c r="K138" s="32"/>
-      <c r="L138" s="32"/>
+      <c r="K138" s="33"/>
+      <c r="L138" s="33"/>
       <c r="M138" s="39"/>
       <c r="N138" s="39"/>
       <c r="O138" s="39"/>
@@ -18922,7 +20895,7 @@
       <c r="AH138" s="39"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="32"/>
+      <c r="A139" s="33"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
       <c r="D139" s="15"/>
@@ -18932,8 +20905,8 @@
       <c r="H139" s="14"/>
       <c r="I139" s="14"/>
       <c r="J139" s="14"/>
-      <c r="K139" s="32"/>
-      <c r="L139" s="32"/>
+      <c r="K139" s="33"/>
+      <c r="L139" s="33"/>
       <c r="M139" s="39"/>
       <c r="N139" s="39"/>
       <c r="O139" s="39"/>
@@ -18958,7 +20931,7 @@
       <c r="AH139" s="39"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="32"/>
+      <c r="A140" s="33"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
       <c r="D140" s="15"/>
@@ -18968,8 +20941,8 @@
       <c r="H140" s="14"/>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
-      <c r="K140" s="32"/>
-      <c r="L140" s="32"/>
+      <c r="K140" s="33"/>
+      <c r="L140" s="33"/>
       <c r="M140" s="39"/>
       <c r="N140" s="39"/>
       <c r="O140" s="39"/>
@@ -18994,7 +20967,7 @@
       <c r="AH140" s="39"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="32"/>
+      <c r="A141" s="33"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
       <c r="D141" s="15"/>
@@ -19004,8 +20977,8 @@
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
-      <c r="K141" s="32"/>
-      <c r="L141" s="32"/>
+      <c r="K141" s="33"/>
+      <c r="L141" s="33"/>
       <c r="M141" s="39"/>
       <c r="N141" s="39"/>
       <c r="O141" s="39"/>
@@ -19030,7 +21003,7 @@
       <c r="AH141" s="39"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="32"/>
+      <c r="A142" s="33"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
       <c r="D142" s="15"/>
@@ -19040,8 +21013,8 @@
       <c r="H142" s="14"/>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
-      <c r="K142" s="32"/>
-      <c r="L142" s="32"/>
+      <c r="K142" s="33"/>
+      <c r="L142" s="33"/>
       <c r="M142" s="39"/>
       <c r="N142" s="39"/>
       <c r="O142" s="39"/>
@@ -19066,7 +21039,7 @@
       <c r="AH142" s="39"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="32"/>
+      <c r="A143" s="33"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
       <c r="D143" s="15"/>
@@ -19076,8 +21049,8 @@
       <c r="H143" s="14"/>
       <c r="I143" s="14"/>
       <c r="J143" s="14"/>
-      <c r="K143" s="32"/>
-      <c r="L143" s="32"/>
+      <c r="K143" s="33"/>
+      <c r="L143" s="33"/>
       <c r="M143" s="39"/>
       <c r="N143" s="39"/>
       <c r="O143" s="39"/>
@@ -19102,7 +21075,7 @@
       <c r="AH143" s="39"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="32"/>
+      <c r="A144" s="33"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
       <c r="D144" s="15"/>
@@ -19112,8 +21085,8 @@
       <c r="H144" s="14"/>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
-      <c r="K144" s="32"/>
-      <c r="L144" s="32"/>
+      <c r="K144" s="33"/>
+      <c r="L144" s="33"/>
       <c r="M144" s="39"/>
       <c r="N144" s="39"/>
       <c r="O144" s="39"/>
@@ -19138,7 +21111,7 @@
       <c r="AH144" s="39"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="32"/>
+      <c r="A145" s="33"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
       <c r="D145" s="15"/>
@@ -19148,8 +21121,8 @@
       <c r="H145" s="14"/>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
-      <c r="K145" s="32"/>
-      <c r="L145" s="32"/>
+      <c r="K145" s="33"/>
+      <c r="L145" s="33"/>
       <c r="M145" s="39"/>
       <c r="N145" s="39"/>
       <c r="O145" s="39"/>
@@ -19174,7 +21147,7 @@
       <c r="AH145" s="39"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="32"/>
+      <c r="A146" s="33"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
       <c r="D146" s="15"/>
@@ -19184,8 +21157,8 @@
       <c r="H146" s="14"/>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
-      <c r="K146" s="32"/>
-      <c r="L146" s="32"/>
+      <c r="K146" s="33"/>
+      <c r="L146" s="33"/>
       <c r="M146" s="39"/>
       <c r="N146" s="39"/>
       <c r="O146" s="39"/>
@@ -19210,7 +21183,7 @@
       <c r="AH146" s="39"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="32"/>
+      <c r="A147" s="33"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
       <c r="D147" s="15"/>
@@ -19220,8 +21193,8 @@
       <c r="H147" s="14"/>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
-      <c r="K147" s="32"/>
-      <c r="L147" s="32"/>
+      <c r="K147" s="33"/>
+      <c r="L147" s="33"/>
       <c r="M147" s="39"/>
       <c r="N147" s="39"/>
       <c r="O147" s="39"/>
@@ -19246,7 +21219,7 @@
       <c r="AH147" s="39"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="32"/>
+      <c r="A148" s="33"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
       <c r="D148" s="15"/>
@@ -19256,8 +21229,8 @@
       <c r="H148" s="14"/>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
-      <c r="K148" s="32"/>
-      <c r="L148" s="32"/>
+      <c r="K148" s="33"/>
+      <c r="L148" s="33"/>
       <c r="M148" s="39"/>
       <c r="N148" s="39"/>
       <c r="O148" s="39"/>
@@ -19282,7 +21255,7 @@
       <c r="AH148" s="39"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="32"/>
+      <c r="A149" s="33"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
       <c r="D149" s="15"/>
@@ -19292,8 +21265,8 @@
       <c r="H149" s="14"/>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
-      <c r="K149" s="32"/>
-      <c r="L149" s="32"/>
+      <c r="K149" s="33"/>
+      <c r="L149" s="33"/>
       <c r="M149" s="39"/>
       <c r="N149" s="39"/>
       <c r="O149" s="39"/>
@@ -19318,7 +21291,7 @@
       <c r="AH149" s="39"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="32"/>
+      <c r="A150" s="33"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
       <c r="D150" s="15"/>
@@ -19328,8 +21301,8 @@
       <c r="H150" s="14"/>
       <c r="I150" s="14"/>
       <c r="J150" s="14"/>
-      <c r="K150" s="32"/>
-      <c r="L150" s="32"/>
+      <c r="K150" s="33"/>
+      <c r="L150" s="33"/>
       <c r="M150" s="39"/>
       <c r="N150" s="39"/>
       <c r="O150" s="39"/>
@@ -19354,7 +21327,7 @@
       <c r="AH150" s="39"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="32"/>
+      <c r="A151" s="33"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
       <c r="D151" s="15"/>
@@ -19364,8 +21337,8 @@
       <c r="H151" s="14"/>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
-      <c r="K151" s="32"/>
-      <c r="L151" s="32"/>
+      <c r="K151" s="33"/>
+      <c r="L151" s="33"/>
       <c r="M151" s="39"/>
       <c r="N151" s="39"/>
       <c r="O151" s="39"/>
@@ -19390,7 +21363,7 @@
       <c r="AH151" s="39"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="32"/>
+      <c r="A152" s="33"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
       <c r="D152" s="15"/>
@@ -19400,8 +21373,8 @@
       <c r="H152" s="14"/>
       <c r="I152" s="14"/>
       <c r="J152" s="14"/>
-      <c r="K152" s="32"/>
-      <c r="L152" s="32"/>
+      <c r="K152" s="33"/>
+      <c r="L152" s="33"/>
       <c r="M152" s="39"/>
       <c r="N152" s="39"/>
       <c r="O152" s="39"/>
@@ -19426,7 +21399,7 @@
       <c r="AH152" s="39"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="32"/>
+      <c r="A153" s="33"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
       <c r="D153" s="15"/>
@@ -19436,8 +21409,8 @@
       <c r="H153" s="14"/>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
-      <c r="K153" s="32"/>
-      <c r="L153" s="32"/>
+      <c r="K153" s="33"/>
+      <c r="L153" s="33"/>
       <c r="M153" s="39"/>
       <c r="N153" s="39"/>
       <c r="O153" s="39"/>
@@ -19462,7 +21435,7 @@
       <c r="AH153" s="39"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="32"/>
+      <c r="A154" s="33"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
       <c r="D154" s="15"/>
@@ -19472,8 +21445,8 @@
       <c r="H154" s="14"/>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
-      <c r="K154" s="32"/>
-      <c r="L154" s="32"/>
+      <c r="K154" s="33"/>
+      <c r="L154" s="33"/>
       <c r="M154" s="39"/>
       <c r="N154" s="39"/>
       <c r="O154" s="39"/>
@@ -19498,7 +21471,7 @@
       <c r="AH154" s="39"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="32"/>
+      <c r="A155" s="33"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
       <c r="D155" s="15"/>
@@ -19508,8 +21481,8 @@
       <c r="H155" s="14"/>
       <c r="I155" s="14"/>
       <c r="J155" s="14"/>
-      <c r="K155" s="32"/>
-      <c r="L155" s="32"/>
+      <c r="K155" s="33"/>
+      <c r="L155" s="33"/>
       <c r="M155" s="39"/>
       <c r="N155" s="39"/>
       <c r="O155" s="39"/>
@@ -19534,7 +21507,7 @@
       <c r="AH155" s="39"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="32"/>
+      <c r="A156" s="33"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
       <c r="D156" s="15"/>
@@ -19544,8 +21517,8 @@
       <c r="H156" s="14"/>
       <c r="I156" s="14"/>
       <c r="J156" s="14"/>
-      <c r="K156" s="32"/>
-      <c r="L156" s="32"/>
+      <c r="K156" s="33"/>
+      <c r="L156" s="33"/>
       <c r="M156" s="39"/>
       <c r="N156" s="39"/>
       <c r="O156" s="39"/>
@@ -19570,7 +21543,7 @@
       <c r="AH156" s="39"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="32"/>
+      <c r="A157" s="33"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
       <c r="D157" s="15"/>
@@ -19580,8 +21553,8 @@
       <c r="H157" s="14"/>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
-      <c r="K157" s="32"/>
-      <c r="L157" s="32"/>
+      <c r="K157" s="33"/>
+      <c r="L157" s="33"/>
       <c r="M157" s="39"/>
       <c r="N157" s="39"/>
       <c r="O157" s="39"/>
@@ -19606,7 +21579,7 @@
       <c r="AH157" s="39"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="32"/>
+      <c r="A158" s="33"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
       <c r="D158" s="15"/>
@@ -19616,8 +21589,8 @@
       <c r="H158" s="14"/>
       <c r="I158" s="14"/>
       <c r="J158" s="14"/>
-      <c r="K158" s="32"/>
-      <c r="L158" s="32"/>
+      <c r="K158" s="33"/>
+      <c r="L158" s="33"/>
       <c r="M158" s="39"/>
       <c r="N158" s="39"/>
       <c r="O158" s="39"/>
@@ -19642,7 +21615,7 @@
       <c r="AH158" s="39"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="32"/>
+      <c r="A159" s="33"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
       <c r="D159" s="15"/>
@@ -19652,8 +21625,8 @@
       <c r="H159" s="14"/>
       <c r="I159" s="14"/>
       <c r="J159" s="14"/>
-      <c r="K159" s="32"/>
-      <c r="L159" s="32"/>
+      <c r="K159" s="33"/>
+      <c r="L159" s="33"/>
       <c r="M159" s="39"/>
       <c r="N159" s="39"/>
       <c r="O159" s="39"/>
@@ -19678,7 +21651,7 @@
       <c r="AH159" s="39"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="32"/>
+      <c r="A160" s="33"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
       <c r="D160" s="15"/>
@@ -19688,8 +21661,8 @@
       <c r="H160" s="14"/>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
-      <c r="K160" s="32"/>
-      <c r="L160" s="32"/>
+      <c r="K160" s="33"/>
+      <c r="L160" s="33"/>
       <c r="M160" s="39"/>
       <c r="N160" s="39"/>
       <c r="O160" s="39"/>
@@ -19714,7 +21687,7 @@
       <c r="AH160" s="39"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="32"/>
+      <c r="A161" s="33"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
       <c r="D161" s="15"/>
@@ -19724,8 +21697,8 @@
       <c r="H161" s="14"/>
       <c r="I161" s="14"/>
       <c r="J161" s="14"/>
-      <c r="K161" s="32"/>
-      <c r="L161" s="32"/>
+      <c r="K161" s="33"/>
+      <c r="L161" s="33"/>
       <c r="M161" s="39"/>
       <c r="N161" s="39"/>
       <c r="O161" s="39"/>
@@ -19750,7 +21723,7 @@
       <c r="AH161" s="39"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="32"/>
+      <c r="A162" s="33"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
       <c r="D162" s="15"/>
@@ -19760,8 +21733,8 @@
       <c r="H162" s="14"/>
       <c r="I162" s="14"/>
       <c r="J162" s="14"/>
-      <c r="K162" s="32"/>
-      <c r="L162" s="32"/>
+      <c r="K162" s="33"/>
+      <c r="L162" s="33"/>
       <c r="M162" s="39"/>
       <c r="N162" s="39"/>
       <c r="O162" s="39"/>
@@ -19786,7 +21759,7 @@
       <c r="AH162" s="39"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="32"/>
+      <c r="A163" s="33"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
       <c r="D163" s="15"/>
@@ -19796,8 +21769,8 @@
       <c r="H163" s="14"/>
       <c r="I163" s="14"/>
       <c r="J163" s="14"/>
-      <c r="K163" s="32"/>
-      <c r="L163" s="32"/>
+      <c r="K163" s="33"/>
+      <c r="L163" s="33"/>
       <c r="M163" s="39"/>
       <c r="N163" s="39"/>
       <c r="O163" s="39"/>
@@ -19822,7 +21795,7 @@
       <c r="AH163" s="39"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="32"/>
+      <c r="A164" s="33"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
       <c r="D164" s="15"/>
@@ -19832,8 +21805,8 @@
       <c r="H164" s="14"/>
       <c r="I164" s="14"/>
       <c r="J164" s="14"/>
-      <c r="K164" s="32"/>
-      <c r="L164" s="32"/>
+      <c r="K164" s="33"/>
+      <c r="L164" s="33"/>
       <c r="M164" s="39"/>
       <c r="N164" s="39"/>
       <c r="O164" s="39"/>
@@ -19858,7 +21831,7 @@
       <c r="AH164" s="39"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="32"/>
+      <c r="A165" s="33"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
       <c r="D165" s="15"/>
@@ -19868,8 +21841,8 @@
       <c r="H165" s="14"/>
       <c r="I165" s="14"/>
       <c r="J165" s="14"/>
-      <c r="K165" s="32"/>
-      <c r="L165" s="32"/>
+      <c r="K165" s="33"/>
+      <c r="L165" s="33"/>
       <c r="M165" s="39"/>
       <c r="N165" s="39"/>
       <c r="O165" s="39"/>
@@ -19894,7 +21867,7 @@
       <c r="AH165" s="39"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="32"/>
+      <c r="A166" s="33"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
       <c r="D166" s="15"/>
@@ -19904,8 +21877,8 @@
       <c r="H166" s="14"/>
       <c r="I166" s="14"/>
       <c r="J166" s="14"/>
-      <c r="K166" s="32"/>
-      <c r="L166" s="32"/>
+      <c r="K166" s="33"/>
+      <c r="L166" s="33"/>
       <c r="M166" s="39"/>
       <c r="N166" s="39"/>
       <c r="O166" s="39"/>
@@ -19930,7 +21903,7 @@
       <c r="AH166" s="39"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="32"/>
+      <c r="A167" s="33"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
       <c r="D167" s="15"/>
@@ -19940,8 +21913,8 @@
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
-      <c r="K167" s="32"/>
-      <c r="L167" s="32"/>
+      <c r="K167" s="33"/>
+      <c r="L167" s="33"/>
       <c r="M167" s="39"/>
       <c r="N167" s="39"/>
       <c r="O167" s="39"/>
@@ -19966,7 +21939,7 @@
       <c r="AH167" s="39"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="32"/>
+      <c r="A168" s="33"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
       <c r="D168" s="15"/>
@@ -19976,8 +21949,8 @@
       <c r="H168" s="14"/>
       <c r="I168" s="14"/>
       <c r="J168" s="14"/>
-      <c r="K168" s="32"/>
-      <c r="L168" s="32"/>
+      <c r="K168" s="33"/>
+      <c r="L168" s="33"/>
       <c r="M168" s="39"/>
       <c r="N168" s="39"/>
       <c r="O168" s="39"/>
@@ -20002,7 +21975,7 @@
       <c r="AH168" s="39"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="32"/>
+      <c r="A169" s="33"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
       <c r="D169" s="15"/>
@@ -20012,8 +21985,8 @@
       <c r="H169" s="14"/>
       <c r="I169" s="14"/>
       <c r="J169" s="14"/>
-      <c r="K169" s="32"/>
-      <c r="L169" s="32"/>
+      <c r="K169" s="33"/>
+      <c r="L169" s="33"/>
       <c r="M169" s="39"/>
       <c r="N169" s="39"/>
       <c r="O169" s="39"/>
@@ -20038,7 +22011,7 @@
       <c r="AH169" s="39"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="32"/>
+      <c r="A170" s="33"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
       <c r="D170" s="15"/>
@@ -20048,8 +22021,8 @@
       <c r="H170" s="14"/>
       <c r="I170" s="14"/>
       <c r="J170" s="14"/>
-      <c r="K170" s="32"/>
-      <c r="L170" s="32"/>
+      <c r="K170" s="33"/>
+      <c r="L170" s="33"/>
       <c r="M170" s="39"/>
       <c r="N170" s="39"/>
       <c r="O170" s="39"/>
@@ -20074,7 +22047,7 @@
       <c r="AH170" s="39"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="32"/>
+      <c r="A171" s="33"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
       <c r="D171" s="15"/>
@@ -20084,8 +22057,8 @@
       <c r="H171" s="14"/>
       <c r="I171" s="14"/>
       <c r="J171" s="14"/>
-      <c r="K171" s="32"/>
-      <c r="L171" s="32"/>
+      <c r="K171" s="33"/>
+      <c r="L171" s="33"/>
       <c r="M171" s="39"/>
       <c r="N171" s="39"/>
       <c r="O171" s="39"/>
@@ -20110,7 +22083,7 @@
       <c r="AH171" s="39"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="32"/>
+      <c r="A172" s="33"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
       <c r="D172" s="15"/>
@@ -20120,8 +22093,8 @@
       <c r="H172" s="14"/>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
-      <c r="K172" s="32"/>
-      <c r="L172" s="32"/>
+      <c r="K172" s="33"/>
+      <c r="L172" s="33"/>
       <c r="M172" s="39"/>
       <c r="N172" s="39"/>
       <c r="O172" s="39"/>
@@ -20146,7 +22119,7 @@
       <c r="AH172" s="39"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="32"/>
+      <c r="A173" s="33"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
       <c r="D173" s="15"/>
@@ -20156,8 +22129,8 @@
       <c r="H173" s="14"/>
       <c r="I173" s="14"/>
       <c r="J173" s="14"/>
-      <c r="K173" s="32"/>
-      <c r="L173" s="32"/>
+      <c r="K173" s="33"/>
+      <c r="L173" s="33"/>
       <c r="M173" s="39"/>
       <c r="N173" s="39"/>
       <c r="O173" s="39"/>
@@ -20182,7 +22155,7 @@
       <c r="AH173" s="39"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="32"/>
+      <c r="A174" s="33"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
       <c r="D174" s="15"/>
@@ -20192,8 +22165,8 @@
       <c r="H174" s="14"/>
       <c r="I174" s="14"/>
       <c r="J174" s="14"/>
-      <c r="K174" s="32"/>
-      <c r="L174" s="32"/>
+      <c r="K174" s="33"/>
+      <c r="L174" s="33"/>
       <c r="M174" s="39"/>
       <c r="N174" s="39"/>
       <c r="O174" s="39"/>
@@ -20218,7 +22191,7 @@
       <c r="AH174" s="39"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="32"/>
+      <c r="A175" s="33"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
       <c r="D175" s="15"/>
@@ -20228,8 +22201,8 @@
       <c r="H175" s="14"/>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
-      <c r="K175" s="32"/>
-      <c r="L175" s="32"/>
+      <c r="K175" s="33"/>
+      <c r="L175" s="33"/>
       <c r="M175" s="39"/>
       <c r="N175" s="39"/>
       <c r="O175" s="39"/>
@@ -20254,7 +22227,7 @@
       <c r="AH175" s="39"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="32"/>
+      <c r="A176" s="33"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
       <c r="D176" s="15"/>
@@ -20264,8 +22237,8 @@
       <c r="H176" s="14"/>
       <c r="I176" s="14"/>
       <c r="J176" s="14"/>
-      <c r="K176" s="32"/>
-      <c r="L176" s="32"/>
+      <c r="K176" s="33"/>
+      <c r="L176" s="33"/>
       <c r="M176" s="39"/>
       <c r="N176" s="39"/>
       <c r="O176" s="39"/>
@@ -20290,7 +22263,7 @@
       <c r="AH176" s="39"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="32"/>
+      <c r="A177" s="33"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
       <c r="D177" s="15"/>
@@ -20300,8 +22273,8 @@
       <c r="H177" s="14"/>
       <c r="I177" s="14"/>
       <c r="J177" s="14"/>
-      <c r="K177" s="32"/>
-      <c r="L177" s="32"/>
+      <c r="K177" s="33"/>
+      <c r="L177" s="33"/>
       <c r="M177" s="39"/>
       <c r="N177" s="39"/>
       <c r="O177" s="39"/>
@@ -20326,7 +22299,7 @@
       <c r="AH177" s="39"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="32"/>
+      <c r="A178" s="33"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
       <c r="D178" s="15"/>
@@ -20336,8 +22309,8 @@
       <c r="H178" s="14"/>
       <c r="I178" s="14"/>
       <c r="J178" s="14"/>
-      <c r="K178" s="32"/>
-      <c r="L178" s="32"/>
+      <c r="K178" s="33"/>
+      <c r="L178" s="33"/>
       <c r="M178" s="39"/>
       <c r="N178" s="39"/>
       <c r="O178" s="39"/>
@@ -20362,7 +22335,7 @@
       <c r="AH178" s="39"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="32"/>
+      <c r="A179" s="33"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
       <c r="D179" s="15"/>
@@ -20372,8 +22345,8 @@
       <c r="H179" s="14"/>
       <c r="I179" s="14"/>
       <c r="J179" s="14"/>
-      <c r="K179" s="32"/>
-      <c r="L179" s="32"/>
+      <c r="K179" s="33"/>
+      <c r="L179" s="33"/>
       <c r="M179" s="39"/>
       <c r="N179" s="39"/>
       <c r="O179" s="39"/>
@@ -20398,7 +22371,7 @@
       <c r="AH179" s="39"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="32"/>
+      <c r="A180" s="33"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
       <c r="D180" s="15"/>
@@ -20408,8 +22381,8 @@
       <c r="H180" s="14"/>
       <c r="I180" s="14"/>
       <c r="J180" s="14"/>
-      <c r="K180" s="32"/>
-      <c r="L180" s="32"/>
+      <c r="K180" s="33"/>
+      <c r="L180" s="33"/>
       <c r="M180" s="39"/>
       <c r="N180" s="39"/>
       <c r="O180" s="39"/>
@@ -20434,7 +22407,7 @@
       <c r="AH180" s="39"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="32"/>
+      <c r="A181" s="33"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
       <c r="D181" s="15"/>
@@ -20444,8 +22417,8 @@
       <c r="H181" s="14"/>
       <c r="I181" s="14"/>
       <c r="J181" s="14"/>
-      <c r="K181" s="32"/>
-      <c r="L181" s="32"/>
+      <c r="K181" s="33"/>
+      <c r="L181" s="33"/>
       <c r="M181" s="39"/>
       <c r="N181" s="39"/>
       <c r="O181" s="39"/>
@@ -20470,7 +22443,7 @@
       <c r="AH181" s="39"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="32"/>
+      <c r="A182" s="33"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
       <c r="D182" s="15"/>
@@ -20480,8 +22453,8 @@
       <c r="H182" s="14"/>
       <c r="I182" s="14"/>
       <c r="J182" s="14"/>
-      <c r="K182" s="32"/>
-      <c r="L182" s="32"/>
+      <c r="K182" s="33"/>
+      <c r="L182" s="33"/>
       <c r="M182" s="39"/>
       <c r="N182" s="39"/>
       <c r="O182" s="39"/>
@@ -20506,7 +22479,7 @@
       <c r="AH182" s="39"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="32"/>
+      <c r="A183" s="33"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
       <c r="D183" s="15"/>
@@ -20516,8 +22489,8 @@
       <c r="H183" s="14"/>
       <c r="I183" s="14"/>
       <c r="J183" s="14"/>
-      <c r="K183" s="32"/>
-      <c r="L183" s="32"/>
+      <c r="K183" s="33"/>
+      <c r="L183" s="33"/>
       <c r="M183" s="39"/>
       <c r="N183" s="39"/>
       <c r="O183" s="39"/>
@@ -20542,7 +22515,7 @@
       <c r="AH183" s="39"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="32"/>
+      <c r="A184" s="33"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
       <c r="D184" s="15"/>
@@ -20552,8 +22525,8 @@
       <c r="H184" s="14"/>
       <c r="I184" s="14"/>
       <c r="J184" s="14"/>
-      <c r="K184" s="32"/>
-      <c r="L184" s="32"/>
+      <c r="K184" s="33"/>
+      <c r="L184" s="33"/>
       <c r="M184" s="39"/>
       <c r="N184" s="39"/>
       <c r="O184" s="39"/>
@@ -20578,7 +22551,7 @@
       <c r="AH184" s="39"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="32"/>
+      <c r="A185" s="33"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
       <c r="D185" s="15"/>
@@ -20588,8 +22561,8 @@
       <c r="H185" s="14"/>
       <c r="I185" s="14"/>
       <c r="J185" s="14"/>
-      <c r="K185" s="32"/>
-      <c r="L185" s="32"/>
+      <c r="K185" s="33"/>
+      <c r="L185" s="33"/>
       <c r="M185" s="39"/>
       <c r="N185" s="39"/>
       <c r="O185" s="39"/>
@@ -20614,7 +22587,7 @@
       <c r="AH185" s="39"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="32"/>
+      <c r="A186" s="33"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
       <c r="D186" s="15"/>
@@ -20624,8 +22597,8 @@
       <c r="H186" s="14"/>
       <c r="I186" s="14"/>
       <c r="J186" s="14"/>
-      <c r="K186" s="32"/>
-      <c r="L186" s="32"/>
+      <c r="K186" s="33"/>
+      <c r="L186" s="33"/>
       <c r="M186" s="39"/>
       <c r="N186" s="39"/>
       <c r="O186" s="39"/>
@@ -20650,7 +22623,7 @@
       <c r="AH186" s="39"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="32"/>
+      <c r="A187" s="33"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
       <c r="D187" s="15"/>
@@ -20660,8 +22633,8 @@
       <c r="H187" s="14"/>
       <c r="I187" s="14"/>
       <c r="J187" s="14"/>
-      <c r="K187" s="32"/>
-      <c r="L187" s="32"/>
+      <c r="K187" s="33"/>
+      <c r="L187" s="33"/>
       <c r="M187" s="39"/>
       <c r="N187" s="39"/>
       <c r="O187" s="39"/>
@@ -20686,7 +22659,7 @@
       <c r="AH187" s="39"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="32"/>
+      <c r="A188" s="33"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
       <c r="D188" s="15"/>
@@ -20696,8 +22669,8 @@
       <c r="H188" s="14"/>
       <c r="I188" s="14"/>
       <c r="J188" s="14"/>
-      <c r="K188" s="32"/>
-      <c r="L188" s="32"/>
+      <c r="K188" s="33"/>
+      <c r="L188" s="33"/>
       <c r="M188" s="39"/>
       <c r="N188" s="39"/>
       <c r="O188" s="39"/>
@@ -20722,7 +22695,7 @@
       <c r="AH188" s="39"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="32"/>
+      <c r="A189" s="33"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
       <c r="D189" s="15"/>
@@ -20732,8 +22705,8 @@
       <c r="H189" s="14"/>
       <c r="I189" s="14"/>
       <c r="J189" s="14"/>
-      <c r="K189" s="32"/>
-      <c r="L189" s="32"/>
+      <c r="K189" s="33"/>
+      <c r="L189" s="33"/>
       <c r="M189" s="39"/>
       <c r="N189" s="39"/>
       <c r="O189" s="39"/>
@@ -20758,7 +22731,7 @@
       <c r="AH189" s="39"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="32"/>
+      <c r="A190" s="33"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
       <c r="D190" s="15"/>
@@ -20768,8 +22741,8 @@
       <c r="H190" s="14"/>
       <c r="I190" s="14"/>
       <c r="J190" s="14"/>
-      <c r="K190" s="32"/>
-      <c r="L190" s="32"/>
+      <c r="K190" s="33"/>
+      <c r="L190" s="33"/>
       <c r="M190" s="39"/>
       <c r="N190" s="39"/>
       <c r="O190" s="39"/>
@@ -20794,7 +22767,7 @@
       <c r="AH190" s="39"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="32"/>
+      <c r="A191" s="33"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
       <c r="D191" s="15"/>
@@ -20804,8 +22777,8 @@
       <c r="H191" s="14"/>
       <c r="I191" s="14"/>
       <c r="J191" s="14"/>
-      <c r="K191" s="32"/>
-      <c r="L191" s="32"/>
+      <c r="K191" s="33"/>
+      <c r="L191" s="33"/>
       <c r="M191" s="39"/>
       <c r="N191" s="39"/>
       <c r="O191" s="39"/>
@@ -20830,7 +22803,7 @@
       <c r="AH191" s="39"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="32"/>
+      <c r="A192" s="33"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
       <c r="D192" s="15"/>
@@ -20840,8 +22813,8 @@
       <c r="H192" s="14"/>
       <c r="I192" s="14"/>
       <c r="J192" s="14"/>
-      <c r="K192" s="32"/>
-      <c r="L192" s="32"/>
+      <c r="K192" s="33"/>
+      <c r="L192" s="33"/>
       <c r="M192" s="39"/>
       <c r="N192" s="39"/>
       <c r="O192" s="39"/>
@@ -20866,7 +22839,7 @@
       <c r="AH192" s="39"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="32"/>
+      <c r="A193" s="33"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
       <c r="D193" s="15"/>
@@ -20876,8 +22849,8 @@
       <c r="H193" s="14"/>
       <c r="I193" s="14"/>
       <c r="J193" s="14"/>
-      <c r="K193" s="32"/>
-      <c r="L193" s="32"/>
+      <c r="K193" s="33"/>
+      <c r="L193" s="33"/>
       <c r="M193" s="39"/>
       <c r="N193" s="39"/>
       <c r="O193" s="39"/>
@@ -20902,7 +22875,7 @@
       <c r="AH193" s="39"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="32"/>
+      <c r="A194" s="33"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
       <c r="D194" s="15"/>
@@ -20912,8 +22885,8 @@
       <c r="H194" s="14"/>
       <c r="I194" s="14"/>
       <c r="J194" s="14"/>
-      <c r="K194" s="32"/>
-      <c r="L194" s="32"/>
+      <c r="K194" s="33"/>
+      <c r="L194" s="33"/>
       <c r="M194" s="39"/>
       <c r="N194" s="39"/>
       <c r="O194" s="39"/>
@@ -20938,7 +22911,7 @@
       <c r="AH194" s="39"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="32"/>
+      <c r="A195" s="33"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
       <c r="D195" s="15"/>
@@ -20948,8 +22921,8 @@
       <c r="H195" s="14"/>
       <c r="I195" s="14"/>
       <c r="J195" s="14"/>
-      <c r="K195" s="32"/>
-      <c r="L195" s="32"/>
+      <c r="K195" s="33"/>
+      <c r="L195" s="33"/>
       <c r="M195" s="39"/>
       <c r="N195" s="39"/>
       <c r="O195" s="39"/>
@@ -20974,7 +22947,7 @@
       <c r="AH195" s="39"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="32"/>
+      <c r="A196" s="33"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
       <c r="D196" s="15"/>
@@ -20984,8 +22957,8 @@
       <c r="H196" s="14"/>
       <c r="I196" s="14"/>
       <c r="J196" s="14"/>
-      <c r="K196" s="32"/>
-      <c r="L196" s="32"/>
+      <c r="K196" s="33"/>
+      <c r="L196" s="33"/>
       <c r="M196" s="39"/>
       <c r="N196" s="39"/>
       <c r="O196" s="39"/>
@@ -21010,7 +22983,7 @@
       <c r="AH196" s="39"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="32"/>
+      <c r="A197" s="33"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
       <c r="D197" s="15"/>
@@ -21020,8 +22993,8 @@
       <c r="H197" s="14"/>
       <c r="I197" s="14"/>
       <c r="J197" s="14"/>
-      <c r="K197" s="32"/>
-      <c r="L197" s="32"/>
+      <c r="K197" s="33"/>
+      <c r="L197" s="33"/>
       <c r="M197" s="39"/>
       <c r="N197" s="39"/>
       <c r="O197" s="39"/>
@@ -21046,7 +23019,7 @@
       <c r="AH197" s="39"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="32"/>
+      <c r="A198" s="33"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
       <c r="D198" s="15"/>
@@ -21056,8 +23029,8 @@
       <c r="H198" s="14"/>
       <c r="I198" s="14"/>
       <c r="J198" s="14"/>
-      <c r="K198" s="32"/>
-      <c r="L198" s="32"/>
+      <c r="K198" s="33"/>
+      <c r="L198" s="33"/>
       <c r="M198" s="39"/>
       <c r="N198" s="39"/>
       <c r="O198" s="39"/>
@@ -21082,7 +23055,7 @@
       <c r="AH198" s="39"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="32"/>
+      <c r="A199" s="33"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
       <c r="D199" s="15"/>
@@ -21092,8 +23065,8 @@
       <c r="H199" s="14"/>
       <c r="I199" s="14"/>
       <c r="J199" s="14"/>
-      <c r="K199" s="32"/>
-      <c r="L199" s="32"/>
+      <c r="K199" s="33"/>
+      <c r="L199" s="33"/>
       <c r="M199" s="39"/>
       <c r="N199" s="39"/>
       <c r="O199" s="39"/>
@@ -21118,7 +23091,7 @@
       <c r="AH199" s="39"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="32"/>
+      <c r="A200" s="33"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
       <c r="D200" s="15"/>
@@ -21128,8 +23101,8 @@
       <c r="H200" s="14"/>
       <c r="I200" s="14"/>
       <c r="J200" s="14"/>
-      <c r="K200" s="32"/>
-      <c r="L200" s="32"/>
+      <c r="K200" s="33"/>
+      <c r="L200" s="33"/>
       <c r="M200" s="39"/>
       <c r="N200" s="39"/>
       <c r="O200" s="39"/>
@@ -21154,7 +23127,7 @@
       <c r="AH200" s="39"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="32"/>
+      <c r="A201" s="33"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
       <c r="D201" s="15"/>
@@ -21164,8 +23137,8 @@
       <c r="H201" s="14"/>
       <c r="I201" s="14"/>
       <c r="J201" s="14"/>
-      <c r="K201" s="32"/>
-      <c r="L201" s="32"/>
+      <c r="K201" s="33"/>
+      <c r="L201" s="33"/>
       <c r="M201" s="39"/>
       <c r="N201" s="39"/>
       <c r="O201" s="39"/>
@@ -21190,7 +23163,7 @@
       <c r="AH201" s="39"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="32"/>
+      <c r="A202" s="33"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
       <c r="D202" s="15"/>
@@ -21200,8 +23173,8 @@
       <c r="H202" s="14"/>
       <c r="I202" s="14"/>
       <c r="J202" s="14"/>
-      <c r="K202" s="32"/>
-      <c r="L202" s="32"/>
+      <c r="K202" s="33"/>
+      <c r="L202" s="33"/>
       <c r="M202" s="39"/>
       <c r="N202" s="39"/>
       <c r="O202" s="39"/>
@@ -21226,7 +23199,7 @@
       <c r="AH202" s="39"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="32"/>
+      <c r="A203" s="33"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
       <c r="D203" s="15"/>
@@ -21236,8 +23209,8 @@
       <c r="H203" s="14"/>
       <c r="I203" s="14"/>
       <c r="J203" s="14"/>
-      <c r="K203" s="32"/>
-      <c r="L203" s="32"/>
+      <c r="K203" s="33"/>
+      <c r="L203" s="33"/>
       <c r="M203" s="39"/>
       <c r="N203" s="39"/>
       <c r="O203" s="39"/>
@@ -21262,7 +23235,7 @@
       <c r="AH203" s="39"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="32"/>
+      <c r="A204" s="33"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
       <c r="D204" s="15"/>
@@ -21272,8 +23245,8 @@
       <c r="H204" s="14"/>
       <c r="I204" s="14"/>
       <c r="J204" s="14"/>
-      <c r="K204" s="32"/>
-      <c r="L204" s="32"/>
+      <c r="K204" s="33"/>
+      <c r="L204" s="33"/>
       <c r="M204" s="39"/>
       <c r="N204" s="39"/>
       <c r="O204" s="39"/>
@@ -21298,7 +23271,7 @@
       <c r="AH204" s="39"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="32"/>
+      <c r="A205" s="33"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
       <c r="D205" s="15"/>
@@ -21308,8 +23281,8 @@
       <c r="H205" s="14"/>
       <c r="I205" s="14"/>
       <c r="J205" s="14"/>
-      <c r="K205" s="32"/>
-      <c r="L205" s="32"/>
+      <c r="K205" s="33"/>
+      <c r="L205" s="33"/>
       <c r="M205" s="39"/>
       <c r="N205" s="39"/>
       <c r="O205" s="39"/>
@@ -21334,7 +23307,7 @@
       <c r="AH205" s="39"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="32"/>
+      <c r="A206" s="33"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
       <c r="D206" s="15"/>
@@ -21344,8 +23317,8 @@
       <c r="H206" s="14"/>
       <c r="I206" s="14"/>
       <c r="J206" s="14"/>
-      <c r="K206" s="32"/>
-      <c r="L206" s="32"/>
+      <c r="K206" s="33"/>
+      <c r="L206" s="33"/>
       <c r="M206" s="39"/>
       <c r="N206" s="39"/>
       <c r="O206" s="39"/>
@@ -21370,7 +23343,7 @@
       <c r="AH206" s="39"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="32"/>
+      <c r="A207" s="33"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
       <c r="D207" s="15"/>
@@ -21380,8 +23353,8 @@
       <c r="H207" s="14"/>
       <c r="I207" s="14"/>
       <c r="J207" s="14"/>
-      <c r="K207" s="32"/>
-      <c r="L207" s="32"/>
+      <c r="K207" s="33"/>
+      <c r="L207" s="33"/>
       <c r="M207" s="39"/>
       <c r="N207" s="39"/>
       <c r="O207" s="39"/>
@@ -21406,7 +23379,7 @@
       <c r="AH207" s="39"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="32"/>
+      <c r="A208" s="33"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
       <c r="D208" s="15"/>
@@ -21416,8 +23389,8 @@
       <c r="H208" s="14"/>
       <c r="I208" s="14"/>
       <c r="J208" s="14"/>
-      <c r="K208" s="32"/>
-      <c r="L208" s="32"/>
+      <c r="K208" s="33"/>
+      <c r="L208" s="33"/>
       <c r="M208" s="39"/>
       <c r="N208" s="39"/>
       <c r="O208" s="39"/>
@@ -21442,7 +23415,7 @@
       <c r="AH208" s="39"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="32"/>
+      <c r="A209" s="33"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
       <c r="D209" s="15"/>
@@ -21452,8 +23425,8 @@
       <c r="H209" s="14"/>
       <c r="I209" s="14"/>
       <c r="J209" s="14"/>
-      <c r="K209" s="32"/>
-      <c r="L209" s="32"/>
+      <c r="K209" s="33"/>
+      <c r="L209" s="33"/>
       <c r="M209" s="39"/>
       <c r="N209" s="39"/>
       <c r="O209" s="39"/>
@@ -21478,7 +23451,7 @@
       <c r="AH209" s="39"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="32"/>
+      <c r="A210" s="33"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
       <c r="D210" s="15"/>
@@ -21488,8 +23461,8 @@
       <c r="H210" s="14"/>
       <c r="I210" s="14"/>
       <c r="J210" s="14"/>
-      <c r="K210" s="32"/>
-      <c r="L210" s="32"/>
+      <c r="K210" s="33"/>
+      <c r="L210" s="33"/>
       <c r="M210" s="39"/>
       <c r="N210" s="39"/>
       <c r="O210" s="39"/>
@@ -21514,7 +23487,7 @@
       <c r="AH210" s="39"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="32"/>
+      <c r="A211" s="33"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
       <c r="D211" s="15"/>
@@ -21524,8 +23497,8 @@
       <c r="H211" s="14"/>
       <c r="I211" s="14"/>
       <c r="J211" s="14"/>
-      <c r="K211" s="32"/>
-      <c r="L211" s="32"/>
+      <c r="K211" s="33"/>
+      <c r="L211" s="33"/>
       <c r="M211" s="39"/>
       <c r="N211" s="39"/>
       <c r="O211" s="39"/>
@@ -21550,7 +23523,7 @@
       <c r="AH211" s="39"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="32"/>
+      <c r="A212" s="33"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
       <c r="D212" s="15"/>
@@ -21560,8 +23533,8 @@
       <c r="H212" s="14"/>
       <c r="I212" s="14"/>
       <c r="J212" s="14"/>
-      <c r="K212" s="32"/>
-      <c r="L212" s="32"/>
+      <c r="K212" s="33"/>
+      <c r="L212" s="33"/>
       <c r="M212" s="39"/>
       <c r="N212" s="39"/>
       <c r="O212" s="39"/>
@@ -21586,7 +23559,7 @@
       <c r="AH212" s="39"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="32"/>
+      <c r="A213" s="33"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
       <c r="D213" s="15"/>
@@ -21596,8 +23569,8 @@
       <c r="H213" s="14"/>
       <c r="I213" s="14"/>
       <c r="J213" s="14"/>
-      <c r="K213" s="32"/>
-      <c r="L213" s="32"/>
+      <c r="K213" s="33"/>
+      <c r="L213" s="33"/>
       <c r="M213" s="39"/>
       <c r="N213" s="39"/>
       <c r="O213" s="39"/>
@@ -21622,7 +23595,7 @@
       <c r="AH213" s="39"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="32"/>
+      <c r="A214" s="33"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
       <c r="D214" s="15"/>
@@ -21632,8 +23605,8 @@
       <c r="H214" s="14"/>
       <c r="I214" s="14"/>
       <c r="J214" s="14"/>
-      <c r="K214" s="32"/>
-      <c r="L214" s="32"/>
+      <c r="K214" s="33"/>
+      <c r="L214" s="33"/>
       <c r="M214" s="39"/>
       <c r="N214" s="39"/>
       <c r="O214" s="39"/>
@@ -21658,7 +23631,7 @@
       <c r="AH214" s="39"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="32"/>
+      <c r="A215" s="33"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
       <c r="D215" s="15"/>
@@ -21668,8 +23641,8 @@
       <c r="H215" s="14"/>
       <c r="I215" s="14"/>
       <c r="J215" s="14"/>
-      <c r="K215" s="32"/>
-      <c r="L215" s="32"/>
+      <c r="K215" s="33"/>
+      <c r="L215" s="33"/>
       <c r="M215" s="39"/>
       <c r="N215" s="39"/>
       <c r="O215" s="39"/>
@@ -21694,7 +23667,7 @@
       <c r="AH215" s="39"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="32"/>
+      <c r="A216" s="33"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
       <c r="D216" s="15"/>
@@ -21704,8 +23677,8 @@
       <c r="H216" s="14"/>
       <c r="I216" s="14"/>
       <c r="J216" s="14"/>
-      <c r="K216" s="32"/>
-      <c r="L216" s="32"/>
+      <c r="K216" s="33"/>
+      <c r="L216" s="33"/>
       <c r="M216" s="39"/>
       <c r="N216" s="39"/>
       <c r="O216" s="39"/>
@@ -21730,7 +23703,7 @@
       <c r="AH216" s="39"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="32"/>
+      <c r="A217" s="33"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
       <c r="D217" s="15"/>
@@ -21740,8 +23713,8 @@
       <c r="H217" s="14"/>
       <c r="I217" s="14"/>
       <c r="J217" s="14"/>
-      <c r="K217" s="32"/>
-      <c r="L217" s="32"/>
+      <c r="K217" s="33"/>
+      <c r="L217" s="33"/>
       <c r="M217" s="39"/>
       <c r="N217" s="39"/>
       <c r="O217" s="39"/>
@@ -21766,7 +23739,7 @@
       <c r="AH217" s="39"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="32"/>
+      <c r="A218" s="33"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
       <c r="D218" s="15"/>
@@ -21776,8 +23749,8 @@
       <c r="H218" s="14"/>
       <c r="I218" s="14"/>
       <c r="J218" s="14"/>
-      <c r="K218" s="32"/>
-      <c r="L218" s="32"/>
+      <c r="K218" s="33"/>
+      <c r="L218" s="33"/>
       <c r="M218" s="39"/>
       <c r="N218" s="39"/>
       <c r="O218" s="39"/>
@@ -21802,7 +23775,7 @@
       <c r="AH218" s="39"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="32"/>
+      <c r="A219" s="33"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
       <c r="D219" s="15"/>
@@ -21812,8 +23785,8 @@
       <c r="H219" s="14"/>
       <c r="I219" s="14"/>
       <c r="J219" s="14"/>
-      <c r="K219" s="32"/>
-      <c r="L219" s="32"/>
+      <c r="K219" s="33"/>
+      <c r="L219" s="33"/>
       <c r="M219" s="39"/>
       <c r="N219" s="39"/>
       <c r="O219" s="39"/>
@@ -21838,7 +23811,7 @@
       <c r="AH219" s="39"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="32"/>
+      <c r="A220" s="33"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
       <c r="D220" s="15"/>
@@ -21848,8 +23821,8 @@
       <c r="H220" s="14"/>
       <c r="I220" s="14"/>
       <c r="J220" s="14"/>
-      <c r="K220" s="32"/>
-      <c r="L220" s="32"/>
+      <c r="K220" s="33"/>
+      <c r="L220" s="33"/>
       <c r="M220" s="39"/>
       <c r="N220" s="39"/>
       <c r="O220" s="39"/>
